--- a/04_DESIGN_TABLES/DesignTable_2501_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2501_SW2.xlsx
@@ -789,13 +789,13 @@
         <v>0.44</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         <v>0.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         <v>0.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
@@ -1299,13 +1299,13 @@
         <v>0.22</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
@@ -1474,13 +1474,13 @@
         <v>0.28</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.32332</v>
+        <v>0.32282</v>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
@@ -1644,13 +1644,13 @@
         <v>0.375</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
@@ -1814,13 +1814,13 @@
         <v>0.44</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
@@ -1984,13 +1984,13 @@
         <v>0.531</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.30657</v>
+        <v>0.30607</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.30657</v>
+        <v>0.30607</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.61315</v>
+        <v>0.61265</v>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
@@ -2159,13 +2159,13 @@
         <v>0.28</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.32332</v>
+        <v>0.32282</v>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
@@ -2329,13 +2329,13 @@
         <v>0.28</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.32332</v>
+        <v>0.32282</v>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
@@ -2499,13 +2499,13 @@
         <v>0.375</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
@@ -2674,13 +2674,13 @@
         <v>0.28125</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.32476</v>
+        <v>0.32426</v>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
@@ -2849,13 +2849,13 @@
         <v>0.44</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
@@ -3019,13 +3019,13 @@
         <v>0.531</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.30657</v>
+        <v>0.30607</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.30657</v>
+        <v>0.30607</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.61315</v>
+        <v>0.61265</v>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
@@ -3194,13 +3194,13 @@
         <v>0.375</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
@@ -3364,13 +3364,13 @@
         <v>0.375</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
@@ -3534,13 +3534,13 @@
         <v>0.53</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.61199</v>
+        <v>0.61149</v>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
@@ -3709,13 +3709,13 @@
         <v>0.656</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.37874</v>
+        <v>0.37824</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.37874</v>
+        <v>0.37824</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.75748</v>
+        <v>0.75698</v>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
@@ -3884,13 +3884,13 @@
         <v>0.44</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
@@ -4054,13 +4054,13 @@
         <v>0.44</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
@@ -4224,13 +4224,13 @@
         <v>0.53</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.61199</v>
+        <v>0.61149</v>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
@@ -4399,13 +4399,13 @@
         <v>0.655</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.7563299999999999</v>
+        <v>0.75583</v>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
@@ -4574,13 +4574,13 @@
         <v>0.53125</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.61343</v>
+        <v>0.61293</v>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
@@ -4749,13 +4749,13 @@
         <v>0.53125</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.61343</v>
+        <v>0.61293</v>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
@@ -4924,13 +4924,13 @@
         <v>0.53125</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AO26" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.61343</v>
+        <v>0.61293</v>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
@@ -5099,13 +5099,13 @@
         <v>0.655</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.7563299999999999</v>
+        <v>0.75583</v>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
@@ -5274,13 +5274,13 @@
         <v>0.8125</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.4691</v>
+        <v>0.4686</v>
       </c>
       <c r="AO28" t="n">
-        <v>0.4691</v>
+        <v>0.4686</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.93819</v>
+        <v>0.93769</v>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
@@ -5449,13 +5449,13 @@
         <v>0.65625</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.7577700000000001</v>
+        <v>0.75727</v>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
@@ -5624,13 +5624,13 @@
         <v>0.65625</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.7577700000000001</v>
+        <v>0.75727</v>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0.65625</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AO31" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.7577700000000001</v>
+        <v>0.75727</v>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
@@ -5974,13 +5974,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AO32" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
@@ -6149,13 +6149,13 @@
         <v>0.9375</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.54127</v>
+        <v>0.54077</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.54127</v>
+        <v>0.54077</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.08253</v>
+        <v>1.08203</v>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
@@ -6324,13 +6324,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AO34" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
@@ -6494,13 +6494,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AO35" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
@@ -6669,13 +6669,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AN36" t="n">
-        <v>0.54271</v>
+        <v>0.54221</v>
       </c>
       <c r="AO36" t="n">
-        <v>0.54271</v>
+        <v>0.54221</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.08542</v>
+        <v>1.08492</v>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
@@ -6844,13 +6844,13 @@
         <v>0.9375</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.54127</v>
+        <v>0.54077</v>
       </c>
       <c r="AO37" t="n">
-        <v>0.54127</v>
+        <v>0.54077</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.08253</v>
+        <v>1.08203</v>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
@@ -7019,13 +7019,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AN38" t="n">
-        <v>0.54271</v>
+        <v>0.54221</v>
       </c>
       <c r="AO38" t="n">
-        <v>0.54271</v>
+        <v>0.54221</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.08542</v>
+        <v>1.08492</v>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
@@ -7189,13 +7189,13 @@
         <v>0.9375</v>
       </c>
       <c r="AN39" t="n">
-        <v>0.54127</v>
+        <v>0.54077</v>
       </c>
       <c r="AO39" t="n">
-        <v>0.54127</v>
+        <v>0.54077</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.08253</v>
+        <v>1.08203</v>
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
@@ -7364,13 +7364,13 @@
         <v>1.25</v>
       </c>
       <c r="AN40" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="AO40" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.44338</v>
+        <v>1.44288</v>
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
@@ -7539,13 +7539,13 @@
         <v>1.25</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="AO41" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.44338</v>
+        <v>1.44288</v>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
@@ -7709,13 +7709,13 @@
         <v>1.25</v>
       </c>
       <c r="AN42" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="AO42" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.44338</v>
+        <v>1.44288</v>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
@@ -7884,13 +7884,13 @@
         <v>0.22</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AO43" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
@@ -8059,13 +8059,13 @@
         <v>0.281</v>
       </c>
       <c r="AN44" t="n">
-        <v>0.16224</v>
+        <v>0.16174</v>
       </c>
       <c r="AO44" t="n">
-        <v>0.16224</v>
+        <v>0.16174</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.32447</v>
+        <v>0.32397</v>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
@@ -8234,13 +8234,13 @@
         <v>0.28125</v>
       </c>
       <c r="AN45" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="AO45" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.32476</v>
+        <v>0.32426</v>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
@@ -8409,13 +8409,13 @@
         <v>0.375</v>
       </c>
       <c r="AN46" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AO46" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
@@ -8584,13 +8584,13 @@
         <v>0.4375</v>
       </c>
       <c r="AN47" t="n">
-        <v>0.25259</v>
+        <v>0.25209</v>
       </c>
       <c r="AO47" t="n">
-        <v>0.25259</v>
+        <v>0.25209</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.50518</v>
+        <v>0.50468</v>
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
@@ -8759,13 +8759,13 @@
         <v>0.53125</v>
       </c>
       <c r="AN48" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AO48" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.61343</v>
+        <v>0.61293</v>
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
@@ -8934,13 +8934,13 @@
         <v>0.65625</v>
       </c>
       <c r="AN49" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AO49" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.7577700000000001</v>
+        <v>0.75727</v>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>

--- a/04_DESIGN_TABLES/DesignTable_2501_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2501_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2731,14 +2731,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2501-06-08-FG</t>
+          <t>2501-06-04-FG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="C14" t="n">
-        <v>0.44</v>
+        <v>0.28125</v>
       </c>
       <c r="D14" t="n">
         <v>0.28125</v>
@@ -2765,34 +2765,34 @@
         <v>37</v>
       </c>
       <c r="L14" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="M14" t="n">
-        <v>0.44</v>
+        <v>0.28125</v>
       </c>
       <c r="N14" t="n">
-        <v>0.40779</v>
+        <v>0.26092</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5337</v>
+        <v>0.4018</v>
       </c>
       <c r="P14" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2163</v>
+        <v>0.1582</v>
       </c>
       <c r="R14" t="n">
         <v>0.3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="T14" t="n">
-        <v>0.53</v>
+        <v>0.28</v>
       </c>
       <c r="U14" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="V14" t="n">
         <v>0.5625</v>
@@ -2813,58 +2813,58 @@
         <v>0.05556</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.81557</v>
+        <v>0.52183</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.5337</v>
+        <v>0.4018</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.40779</v>
+        <v>0.26092</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.35064</v>
+        <v>0.21647</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.88</v>
+        <v>0.5625</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.664</v>
+        <v>0.504</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.88</v>
+        <v>0.5625</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.72</v>
+        <v>0.53</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.44</v>
+        <v>0.28125</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.44</v>
+        <v>0.28125</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.25353</v>
+        <v>0.16188</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.25353</v>
+        <v>0.16188</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.50757</v>
+        <v>0.32426</v>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>2501-06-08-FG</t>
+          <t>2501-06-04-FG</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 9/16-18 JIC x 1/2-14 NPTF</t>
+          <t>90 deg Male Elbow, 9/16-18 JIC x 1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>VERIFIED-CORE</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -2892,23 +2892,28 @@
           <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p023-t01: agrees on M@DRIVE, N@DRIVE, Y@REF, D@BORE, D1@DRILL | hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
+        </is>
+      </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>2501-06-08-FG</t>
+          <t>2501-06-04-FG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2501-06-12-FG</t>
+          <t>2501-06-06-FG</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="C15" t="n">
-        <v>0.531</v>
+        <v>0.375</v>
       </c>
       <c r="D15" t="n">
         <v>0.28125</v>
@@ -2935,34 +2940,34 @@
         <v>37</v>
       </c>
       <c r="L15" t="n">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="M15" t="n">
-        <v>0.531</v>
+        <v>0.375</v>
       </c>
       <c r="N15" t="n">
-        <v>0.51241</v>
+        <v>0.32823</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5457</v>
+        <v>0.4078</v>
       </c>
       <c r="P15" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2043</v>
+        <v>0.1522</v>
       </c>
       <c r="R15" t="n">
-        <v>0.297</v>
+        <v>0.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="T15" t="n">
-        <v>0.719</v>
+        <v>0.41</v>
       </c>
       <c r="U15" t="n">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="V15" t="n">
         <v>0.5625</v>
@@ -2983,58 +2988,58 @@
         <v>0.05556</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.02482</v>
+        <v>0.65645</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.5457</v>
+        <v>0.4078</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.51241</v>
+        <v>0.32823</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.45527</v>
+        <v>0.28378</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.062</v>
+        <v>0.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.754</v>
+        <v>0.584</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.062</v>
+        <v>0.75</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.84</v>
+        <v>0.66</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.531</v>
+        <v>0.375</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.531</v>
+        <v>0.375</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.30607</v>
+        <v>0.21601</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.30607</v>
+        <v>0.21601</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.61265</v>
+        <v>0.43251</v>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>2501-06-12-FG</t>
+          <t>2501-06-06-FG</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 9/16-18 JIC x 3/4-14 NPTF</t>
+          <t>90 deg Male Elbow, 9/16-18 JIC x 3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -3049,59 +3054,59 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-06-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N673 M 1 Size = 1.31 (table had empty); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P673 L 1 Size = 1.59 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R673 Hex Flat = 1.062 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S673 Side 1 ID = 0.297 (table had empty); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X673 Side 2 ID = 0.719 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p23 2501-FG (same source as OMi, not a second source); JIC end: MS33656J chain per dash (gen_straight2 JIC[6], 2403 table, = Brennan, VERIFIED) incl. THDMAJ_A 0.5625; NPTF end: ASME B1.20.3 (ms51500.NPTF[12]) incl. PIPEOD 1.05; end threads from the part number dashes (= catalog B1 / A2 callouts); dims NOT taken from the non-FG Air-Way twin 2501-06-12 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-06-12 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p23 2501-FG on all five body values, same source), not from the non-FG twin 2501-06-12 | leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0620 (round end flush with the flats by 0.0015; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p023-t01: agrees on M@DRIVE, N@DRIVE, Y@REF, D@BORE, D1@DRILL</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2501-06-12-FG</t>
+          <t>2501-06-06-FG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2501-08-04-FG</t>
+          <t>2501-06-08-FG</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="C16" t="n">
-        <v>0.375</v>
+        <v>0.44</v>
       </c>
       <c r="D16" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="E16" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2837</v>
+        <v>0.2515</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3295</v>
+        <v>0.2405</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0984</v>
+        <v>0.0898</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="J16" t="n">
         <v>60</v>
@@ -3110,106 +3115,106 @@
         <v>37</v>
       </c>
       <c r="L16" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="M16" t="n">
-        <v>0.375</v>
+        <v>0.44</v>
       </c>
       <c r="N16" t="n">
-        <v>0.26092</v>
+        <v>0.40779</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4018</v>
+        <v>0.5337</v>
       </c>
       <c r="P16" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1582</v>
+        <v>0.2163</v>
       </c>
       <c r="R16" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>0.28</v>
+        <v>0.53</v>
       </c>
       <c r="U16" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="V16" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="X16" t="n">
-        <v>0.2837</v>
+        <v>0.2515</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.52183</v>
+        <v>0.81557</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.4018</v>
+        <v>0.5337</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.05556</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.26092</v>
+        <v>0.40779</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.21647</v>
+        <v>0.35064</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.593</v>
+        <v>0.664</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.375</v>
+        <v>0.44</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.375</v>
+        <v>0.44</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.21601</v>
+        <v>0.25353</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.21601</v>
+        <v>0.25353</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.43251</v>
+        <v>0.50757</v>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>2501-08-04-FG</t>
+          <t>2501-06-08-FG</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 3/4-16 JIC x 1/4-18 NPTF</t>
+          <t>90 deg Male Elbow, 9/16-18 JIC x 1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -3219,12 +3224,12 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>3/4-16 JIC</t>
+          <t>9/16-18 JIC</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3239,39 +3244,39 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2501-08-04-FG</t>
+          <t>2501-06-08-FG</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2501-08-06-FG</t>
+          <t>2501-06-12-FG</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="C17" t="n">
-        <v>0.375</v>
+        <v>0.531</v>
       </c>
       <c r="D17" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="E17" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2837</v>
+        <v>0.2515</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3295</v>
+        <v>0.2405</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0984</v>
+        <v>0.0898</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="J17" t="n">
         <v>60</v>
@@ -3280,106 +3285,106 @@
         <v>37</v>
       </c>
       <c r="L17" t="n">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="M17" t="n">
-        <v>0.375</v>
+        <v>0.531</v>
       </c>
       <c r="N17" t="n">
-        <v>0.32823</v>
+        <v>0.51241</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4078</v>
+        <v>0.5457</v>
       </c>
       <c r="P17" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1522</v>
+        <v>0.2043</v>
       </c>
       <c r="R17" t="n">
-        <v>0.39</v>
+        <v>0.297</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T17" t="n">
-        <v>0.41</v>
+        <v>0.719</v>
       </c>
       <c r="U17" t="n">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="V17" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2837</v>
+        <v>0.2515</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.65645</v>
+        <v>1.02482</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.4078</v>
+        <v>0.5457</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.05556</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.32823</v>
+        <v>0.51241</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.28378</v>
+        <v>0.45527</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.75</v>
+        <v>1.062</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.593</v>
+        <v>0.754</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.75</v>
+        <v>1.062</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.66</v>
+        <v>0.84</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.375</v>
+        <v>0.531</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.375</v>
+        <v>0.531</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.21601</v>
+        <v>0.30607</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.21601</v>
+        <v>0.30607</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.43251</v>
+        <v>0.61265</v>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>2501-08-06-FG</t>
+          <t>2501-06-12-FG</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 3/4-16 JIC x 3/8-18 NPTF</t>
+          <t>90 deg Male Elbow, 9/16-18 JIC x 3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -3389,41 +3394,46 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>3/4-16 JIC</t>
+          <t>9/16-18 JIC</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>VERIFIED-CORE</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-06-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N673 M 1 Size = 1.31 (table had empty); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P673 L 1 Size = 1.59 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R673 Hex Flat = 1.062 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S673 Side 1 ID = 0.297 (table had empty); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X673 Side 2 ID = 0.719 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p23 2501-FG (same source as OMi, not a second source); JIC end: MS33656J chain per dash (gen_straight2 JIC[6], 2403 table, = Brennan, VERIFIED) incl. THDMAJ_A 0.5625; NPTF end: ASME B1.20.3 (ms51500.NPTF[12]) incl. PIPEOD 1.05; end threads from the part number dashes (= catalog B1 / A2 callouts); dims NOT taken from the non-FG Air-Way twin 2501-06-12 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-06-12 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p23 2501-FG on all five body values, same source), not from the non-FG twin 2501-06-12 | leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0620 (round end flush with the flats by 0.0015; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2501-08-06-FG</t>
+          <t>2501-06-12-FG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2501-08-12-FG</t>
+          <t>2501-08-04-FG</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="C18" t="n">
-        <v>0.53</v>
+        <v>0.375</v>
       </c>
       <c r="D18" t="n">
         <v>0.375</v>
@@ -3450,34 +3460,34 @@
         <v>37</v>
       </c>
       <c r="L18" t="n">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="M18" t="n">
-        <v>0.53</v>
+        <v>0.375</v>
       </c>
       <c r="N18" t="n">
-        <v>0.51241</v>
+        <v>0.26092</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5457</v>
+        <v>0.4018</v>
       </c>
       <c r="P18" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2043</v>
+        <v>0.1582</v>
       </c>
       <c r="R18" t="n">
         <v>0.39</v>
       </c>
       <c r="S18" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>0.72</v>
+        <v>0.28</v>
       </c>
       <c r="U18" t="n">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="V18" t="n">
         <v>0.75</v>
@@ -3498,58 +3508,58 @@
         <v>0.0625</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.02482</v>
+        <v>0.52183</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.5457</v>
+        <v>0.4018</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.51241</v>
+        <v>0.26092</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.45527</v>
+        <v>0.21647</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.06</v>
+        <v>0.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.763</v>
+        <v>0.593</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.06</v>
+        <v>0.75</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.84</v>
+        <v>0.66</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.53</v>
+        <v>0.375</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.53</v>
+        <v>0.375</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.3055</v>
+        <v>0.21601</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.3055</v>
+        <v>0.21601</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.61149</v>
+        <v>0.43251</v>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>2501-08-12-FG</t>
+          <t>2501-08-04-FG</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 3/4-16 JIC x 3/4-14 NPTF</t>
+          <t>90 deg Male Elbow, 3/4-16 JIC x 1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -3564,7 +3574,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -3577,28 +3587,23 @@
           <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
-        </is>
-      </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2501-08-12-FG</t>
+          <t>2501-08-04-FG</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2501-08-16-FG</t>
+          <t>2501-08-06-FG</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="C19" t="n">
-        <v>0.656</v>
+        <v>0.375</v>
       </c>
       <c r="D19" t="n">
         <v>0.375</v>
@@ -3625,34 +3630,34 @@
         <v>37</v>
       </c>
       <c r="L19" t="n">
-        <v>1.97</v>
+        <v>1.22</v>
       </c>
       <c r="M19" t="n">
-        <v>0.656</v>
+        <v>0.375</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.32823</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6828</v>
+        <v>0.4078</v>
       </c>
       <c r="P19" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.2572</v>
+        <v>0.1522</v>
       </c>
       <c r="R19" t="n">
-        <v>0.391</v>
+        <v>0.39</v>
       </c>
       <c r="S19" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="U19" t="n">
-        <v>1.97</v>
+        <v>1.22</v>
       </c>
       <c r="V19" t="n">
         <v>0.75</v>
@@ -3673,58 +3678,58 @@
         <v>0.0625</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.2832</v>
+        <v>0.65645</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.6828</v>
+        <v>0.4078</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.08696</v>
+        <v>0.05556</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.32823</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.57203</v>
+        <v>0.28378</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.97</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.312</v>
+        <v>0.75</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.863</v>
+        <v>0.593</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.312</v>
+        <v>0.75</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.03</v>
+        <v>0.66</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.656</v>
+        <v>0.375</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.656</v>
+        <v>0.375</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.37824</v>
+        <v>0.21601</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.37824</v>
+        <v>0.21601</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.75698</v>
+        <v>0.43251</v>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>2501-08-16-FG</t>
+          <t>2501-08-06-FG</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 3/4-16 JIC x 1-11 1/2 NPTF</t>
+          <t>90 deg Male Elbow, 3/4-16 JIC x 3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -3739,56 +3744,51 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED-CORE</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-08-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N678 M 1 Size = 1.52 (table had empty); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P678 L 1 Size = 1.97 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R678 Hex Flat = 1.312 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S678 Side 1 ID = 0.391 (table had empty); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X678 Side 2 ID = 0.938 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p23 2501-FG (same source as OMi, not a second source); JIC end: MS33656J chain per dash (gen_straight2 JIC[8], 2403 table, = Brennan, VERIFIED) incl. THDMAJ_A 0.75; NPTF end: ASME B1.20.3 (ms51500.NPTF[16]) incl. PIPEOD 1.315; end threads from the part number dashes (= catalog B1 / A2 callouts); dims NOT taken from the non-FG Air-Way twin 2501-08-16 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-08-16 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p23 2501-FG on all five body values, same source), not from the non-FG twin 2501-08-16 | leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3120 (round end proud of the flats by 0.0069; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2501-08-16-FG</t>
+          <t>2501-08-06-FG</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2501-10-06-FG</t>
+          <t>2501-08-12-FG</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="C20" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="E20" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="G20" t="n">
-        <v>0.386</v>
+        <v>0.3295</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1114</v>
+        <v>0.0984</v>
       </c>
       <c r="I20" t="n">
         <v>0.1546</v>
@@ -3800,106 +3800,106 @@
         <v>37</v>
       </c>
       <c r="L20" t="n">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="M20" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="N20" t="n">
-        <v>0.32823</v>
+        <v>0.51241</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4078</v>
+        <v>0.5457</v>
       </c>
       <c r="P20" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1522</v>
+        <v>0.2043</v>
       </c>
       <c r="R20" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="S20" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T20" t="n">
-        <v>0.41</v>
+        <v>0.72</v>
       </c>
       <c r="U20" t="n">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="V20" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="W20" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.02482</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="AD20" t="n">
         <v>0.07142999999999999</v>
       </c>
-      <c r="X20" t="n">
-        <v>0.3553</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.03866</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0.01786</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.07142999999999999</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0.65645</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.4078</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0.05556</v>
-      </c>
       <c r="AE20" t="n">
-        <v>0.32823</v>
+        <v>0.51241</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.28378</v>
+        <v>0.45527</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.763</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.25353</v>
+        <v>0.3055</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.25353</v>
+        <v>0.3055</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.50757</v>
+        <v>0.61149</v>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>2501-10-06-FG</t>
+          <t>2501-08-12-FG</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 7/8-14 JIC x 3/8-18 NPTF</t>
+          <t>90 deg Male Elbow, 3/4-16 JIC x 3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>7/8-14 JIC</t>
+          <t>3/4-16 JIC</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -3927,38 +3927,43 @@
           <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>2501-10-06-FG</t>
+          <t>2501-08-12-FG</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2501-10-08-FG</t>
+          <t>2501-08-16-FG</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="C21" t="n">
-        <v>0.44</v>
+        <v>0.656</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="E21" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="G21" t="n">
-        <v>0.386</v>
+        <v>0.3295</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1114</v>
+        <v>0.0984</v>
       </c>
       <c r="I21" t="n">
         <v>0.1546</v>
@@ -3970,106 +3975,106 @@
         <v>37</v>
       </c>
       <c r="L21" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="M21" t="n">
-        <v>0.44</v>
+        <v>0.656</v>
       </c>
       <c r="N21" t="n">
-        <v>0.40779</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5337</v>
+        <v>0.6828</v>
       </c>
       <c r="P21" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2163</v>
+        <v>0.2572</v>
       </c>
       <c r="R21" t="n">
-        <v>0.48</v>
+        <v>0.391</v>
       </c>
       <c r="S21" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="T21" t="n">
-        <v>0.53</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="V21" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="W21" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.81557</v>
+        <v>1.2832</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.5337</v>
+        <v>0.6828</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.08696</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.40779</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.35064</v>
+        <v>0.57203</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.88</v>
+        <v>1.312</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.863</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.88</v>
+        <v>1.312</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.72</v>
+        <v>1.03</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.44</v>
+        <v>0.656</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.44</v>
+        <v>0.656</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.25353</v>
+        <v>0.37824</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.25353</v>
+        <v>0.37824</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.50757</v>
+        <v>0.75698</v>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>2501-10-08-FG</t>
+          <t>2501-08-16-FG</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 7/8-14 JIC x 1/2-14 NPTF</t>
+          <t>90 deg Male Elbow, 3/4-16 JIC x 1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -4079,41 +4084,46 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>7/8-14 JIC</t>
+          <t>3/4-16 JIC</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>VERIFIED-CORE</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-08-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N678 M 1 Size = 1.52 (table had empty); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P678 L 1 Size = 1.97 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R678 Hex Flat = 1.312 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S678 Side 1 ID = 0.391 (table had empty); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X678 Side 2 ID = 0.938 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p23 2501-FG (same source as OMi, not a second source); JIC end: MS33656J chain per dash (gen_straight2 JIC[8], 2403 table, = Brennan, VERIFIED) incl. THDMAJ_A 0.75; NPTF end: ASME B1.20.3 (ms51500.NPTF[16]) incl. PIPEOD 1.315; end threads from the part number dashes (= catalog B1 / A2 callouts); dims NOT taken from the non-FG Air-Way twin 2501-08-16 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-08-16 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p23 2501-FG on all five body values, same source), not from the non-FG twin 2501-08-16 | leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3120 (round end proud of the flats by 0.0069; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>2501-10-08-FG</t>
+          <t>2501-08-16-FG</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2501-10-12-FG</t>
+          <t>2501-10-06-FG</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="C22" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="D22" t="n">
         <v>0.4375</v>
@@ -4140,34 +4150,34 @@
         <v>37</v>
       </c>
       <c r="L22" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="M22" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="N22" t="n">
-        <v>0.51241</v>
+        <v>0.32823</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5457</v>
+        <v>0.4078</v>
       </c>
       <c r="P22" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.2043</v>
+        <v>0.1522</v>
       </c>
       <c r="R22" t="n">
         <v>0.48</v>
       </c>
       <c r="S22" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="T22" t="n">
-        <v>0.72</v>
+        <v>0.41</v>
       </c>
       <c r="U22" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
         <v>0.875</v>
@@ -4188,58 +4198,58 @@
         <v>0.07142999999999999</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.02482</v>
+        <v>0.65645</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.5457</v>
+        <v>0.4078</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.51241</v>
+        <v>0.32823</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.45527</v>
+        <v>0.28378</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.782</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.3055</v>
+        <v>0.25353</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.3055</v>
+        <v>0.25353</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.61149</v>
+        <v>0.50757</v>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>2501-10-12-FG</t>
+          <t>2501-10-06-FG</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 7/8-14 JIC x 3/4-14 NPTF</t>
+          <t>90 deg Male Elbow, 7/8-14 JIC x 3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -4254,7 +4264,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -4267,28 +4277,23 @@
           <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
-        </is>
-      </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>2501-10-12-FG</t>
+          <t>2501-10-06-FG</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2501-10-16-FG</t>
+          <t>2501-10-08-FG</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="C23" t="n">
-        <v>0.655</v>
+        <v>0.44</v>
       </c>
       <c r="D23" t="n">
         <v>0.4375</v>
@@ -4315,34 +4320,34 @@
         <v>37</v>
       </c>
       <c r="L23" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="M23" t="n">
-        <v>0.655</v>
+        <v>0.44</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.40779</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6828</v>
+        <v>0.5337</v>
       </c>
       <c r="P23" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2572</v>
+        <v>0.2163</v>
       </c>
       <c r="R23" t="n">
         <v>0.48</v>
       </c>
       <c r="S23" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="U23" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
         <v>0.875</v>
@@ -4363,58 +4368,58 @@
         <v>0.07142999999999999</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.2832</v>
+        <v>0.81557</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.6828</v>
+        <v>0.5337</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.40779</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.57203</v>
+        <v>0.35064</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.31</v>
+        <v>0.88</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.882</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.31</v>
+        <v>0.88</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.03</v>
+        <v>0.72</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.655</v>
+        <v>0.44</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.655</v>
+        <v>0.44</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.37766</v>
+        <v>0.25353</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.37766</v>
+        <v>0.25353</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.75583</v>
+        <v>0.50757</v>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>2501-10-16-FG</t>
+          <t>2501-10-08-FG</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 7/8-14 JIC x 1-11 1/2 NPTF</t>
+          <t>90 deg Male Elbow, 7/8-14 JIC x 1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -4429,7 +4434,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -4442,46 +4447,41 @@
           <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
-        </is>
-      </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2501-10-16-FG</t>
+          <t>2501-10-08-FG</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2501-12-06-FG</t>
+          <t>2501-10-12-FG</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="C24" t="n">
-        <v>0.53125</v>
+        <v>0.53</v>
       </c>
       <c r="D24" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="E24" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="J24" t="n">
         <v>60</v>
@@ -4490,106 +4490,106 @@
         <v>37</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="M24" t="n">
-        <v>0.53125</v>
+        <v>0.53</v>
       </c>
       <c r="N24" t="n">
-        <v>0.32823</v>
+        <v>0.51241</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4078</v>
+        <v>0.5457</v>
       </c>
       <c r="P24" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1522</v>
+        <v>0.2043</v>
       </c>
       <c r="R24" t="n">
-        <v>0.609</v>
+        <v>0.48</v>
       </c>
       <c r="S24" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="T24" t="n">
-        <v>0.406</v>
+        <v>0.72</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="V24" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="W24" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.65645</v>
+        <v>1.02482</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.4078</v>
+        <v>0.5457</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.05556</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.32823</v>
+        <v>0.51241</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.28378</v>
+        <v>0.45527</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.0625</v>
+        <v>1.06</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.796</v>
+        <v>0.782</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.0625</v>
+        <v>1.06</v>
       </c>
       <c r="AK24" t="n">
         <v>0.84</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.53125</v>
+        <v>0.53</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.53125</v>
+        <v>0.53</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.30622</v>
+        <v>0.3055</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.30622</v>
+        <v>0.3055</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.61293</v>
+        <v>0.61149</v>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>2501-12-06-FG</t>
+          <t>2501-10-12-FG</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 1/16-12 JIC x 3/8-18 NPTF</t>
+          <t>90 deg Male Elbow, 7/8-14 JIC x 3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -4599,64 +4599,64 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>7/8-14 JIC</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED-CORE</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-12-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N683 M 1 Size = 1.66 (table had empty); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P683 L 1 Size = 1.40 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R683 Hex Flat = 1.062 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S683 Side 1 ID = 0.609 (table had empty); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X683 Side 2 ID = 0.406 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p23 2501-FG (same source as OMi, not a second source); JIC end: MS33656J chain per dash (gen_straight2 JIC[12], 2403 table, = Brennan, VERIFIED) incl. THDMAJ_A 1.0625; NPTF end: ASME B1.20.3 (ms51500.NPTF[6]) incl. PIPEOD 0.675; end threads from the part number dashes (= catalog B1 / A2 callouts); dims NOT taken from the non-FG Air-Way twin 2501-12-06 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-12-06 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p23 2501-FG on all five body values, same source), not from the non-FG twin 2501-12-06 | hex A/F raised from Air-Way 1.062 to 1.0625 (JIC thread major; 2603HX rule)</t>
+          <t>leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>2501-12-06-FG</t>
+          <t>2501-10-12-FG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2501-12-08-FG</t>
+          <t>2501-10-16-FG</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="C25" t="n">
-        <v>0.53125</v>
+        <v>0.655</v>
       </c>
       <c r="D25" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="E25" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="J25" t="n">
         <v>60</v>
@@ -4665,106 +4665,106 @@
         <v>37</v>
       </c>
       <c r="L25" t="n">
-        <v>1.59</v>
+        <v>1.97</v>
       </c>
       <c r="M25" t="n">
-        <v>0.53125</v>
+        <v>0.655</v>
       </c>
       <c r="N25" t="n">
-        <v>0.40779</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5337</v>
+        <v>0.6828</v>
       </c>
       <c r="P25" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.2163</v>
+        <v>0.2572</v>
       </c>
       <c r="R25" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="S25" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="T25" t="n">
-        <v>0.53</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>1.59</v>
+        <v>1.97</v>
       </c>
       <c r="V25" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="W25" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.81557</v>
+        <v>1.2832</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.5337</v>
+        <v>0.6828</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.08696</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.40779</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.35064</v>
+        <v>0.57203</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.59</v>
+        <v>1.97</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.0625</v>
+        <v>1.31</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.796</v>
+        <v>0.882</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.0625</v>
+        <v>1.31</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.84</v>
+        <v>1.03</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.53125</v>
+        <v>0.655</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.53125</v>
+        <v>0.655</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.30622</v>
+        <v>0.37766</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.30622</v>
+        <v>0.37766</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.61293</v>
+        <v>0.75583</v>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>2501-12-08-FG</t>
+          <t>2501-10-16-FG</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 1/16-12 JIC x 1/2-14 NPTF</t>
+          <t>90 deg Male Elbow, 7/8-14 JIC x 1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>7/8-14 JIC</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -4794,19 +4794,19 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule)</t>
+          <t>leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>2501-12-08-FG</t>
+          <t>2501-10-16-FG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2501-12-12-FG</t>
+          <t>2501-12-06-FG</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -4840,34 +4840,34 @@
         <v>37</v>
       </c>
       <c r="L26" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
         <v>0.53125</v>
       </c>
       <c r="N26" t="n">
-        <v>0.51241</v>
+        <v>0.32823</v>
       </c>
       <c r="O26" t="n">
-        <v>0.5457</v>
+        <v>0.4078</v>
       </c>
       <c r="P26" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.2043</v>
+        <v>0.1522</v>
       </c>
       <c r="R26" t="n">
-        <v>0.61</v>
+        <v>0.609</v>
       </c>
       <c r="S26" t="n">
         <v>1.66</v>
       </c>
       <c r="T26" t="n">
-        <v>0.72</v>
+        <v>0.406</v>
       </c>
       <c r="U26" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
         <v>1.0625</v>
@@ -4888,22 +4888,22 @@
         <v>0.08333</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.02482</v>
+        <v>0.65645</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.5457</v>
+        <v>0.4078</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.51241</v>
+        <v>0.32823</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.45527</v>
+        <v>0.28378</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
         <v>1.0625</v>
@@ -4934,12 +4934,12 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>2501-12-12-FG</t>
+          <t>2501-12-06-FG</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 1/16-12 JIC x 3/4-14 NPTF</t>
+          <t>90 deg Male Elbow, 1 1/16-12 JIC x 3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -4954,41 +4954,41 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>VERIFIED-CORE</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-12-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N683 M 1 Size = 1.66 (table had empty); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P683 L 1 Size = 1.40 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R683 Hex Flat = 1.062 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S683 Side 1 ID = 0.609 (table had empty); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X683 Side 2 ID = 0.406 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p23 2501-FG (same source as OMi, not a second source); JIC end: MS33656J chain per dash (gen_straight2 JIC[12], 2403 table, = Brennan, VERIFIED) incl. THDMAJ_A 1.0625; NPTF end: ASME B1.20.3 (ms51500.NPTF[6]) incl. PIPEOD 0.675; end threads from the part number dashes (= catalog B1 / A2 callouts); dims NOT taken from the non-FG Air-Way twin 2501-12-06 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0625 (round end flush with the flats by 0.0018; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-12-06 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p23 2501-FG on all five body values, same source), not from the non-FG twin 2501-12-06 | hex A/F raised from Air-Way 1.062 to 1.0625 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>2501-12-12-FG</t>
+          <t>2501-12-06-FG</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2501-12-16-FG</t>
+          <t>2501-12-08-FG</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="C27" t="n">
-        <v>0.655</v>
+        <v>0.53125</v>
       </c>
       <c r="D27" t="n">
         <v>0.53125</v>
@@ -5015,34 +5015,34 @@
         <v>37</v>
       </c>
       <c r="L27" t="n">
-        <v>1.97</v>
+        <v>1.59</v>
       </c>
       <c r="M27" t="n">
-        <v>0.655</v>
+        <v>0.53125</v>
       </c>
       <c r="N27" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.40779</v>
       </c>
       <c r="O27" t="n">
-        <v>0.6828</v>
+        <v>0.5337</v>
       </c>
       <c r="P27" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.2572</v>
+        <v>0.2163</v>
       </c>
       <c r="R27" t="n">
         <v>0.61</v>
       </c>
       <c r="S27" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="T27" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="U27" t="n">
-        <v>1.97</v>
+        <v>1.59</v>
       </c>
       <c r="V27" t="n">
         <v>1.0625</v>
@@ -5063,58 +5063,58 @@
         <v>0.08333</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.2832</v>
+        <v>0.81557</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.6828</v>
+        <v>0.5337</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.40779</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.57203</v>
+        <v>0.35064</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.97</v>
+        <v>1.59</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.31</v>
+        <v>1.0625</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.896</v>
+        <v>0.796</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.31</v>
+        <v>1.0625</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.03</v>
+        <v>0.84</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.655</v>
+        <v>0.53125</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.655</v>
+        <v>0.53125</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.37766</v>
+        <v>0.30622</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.37766</v>
+        <v>0.30622</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.75583</v>
+        <v>0.61293</v>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>2501-12-16-FG</t>
+          <t>2501-12-08-FG</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 1/16-12 JIC x 1-11 1/2 NPTF</t>
+          <t>90 deg Male Elbow, 1 1/16-12 JIC x 1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5144,26 +5144,26 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>2501-12-16-FG</t>
+          <t>2501-12-08-FG</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2501-12-20-FG</t>
+          <t>2501-12-12-FG</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.97</v>
+        <v>1.66</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="D28" t="n">
         <v>0.53125</v>
@@ -5190,34 +5190,34 @@
         <v>37</v>
       </c>
       <c r="L28" t="n">
-        <v>2.38</v>
+        <v>1.59</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="N28" t="n">
-        <v>0.81335</v>
+        <v>0.51241</v>
       </c>
       <c r="O28" t="n">
-        <v>0.7068</v>
+        <v>0.5457</v>
       </c>
       <c r="P28" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.2632</v>
+        <v>0.2043</v>
       </c>
       <c r="R28" t="n">
-        <v>0.609</v>
+        <v>0.61</v>
       </c>
       <c r="S28" t="n">
-        <v>1.97</v>
+        <v>1.66</v>
       </c>
       <c r="T28" t="n">
-        <v>1.25</v>
+        <v>0.72</v>
       </c>
       <c r="U28" t="n">
-        <v>2.38</v>
+        <v>1.59</v>
       </c>
       <c r="V28" t="n">
         <v>1.0625</v>
@@ -5238,58 +5238,58 @@
         <v>0.08333</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6267</v>
+        <v>1.02482</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.7068</v>
+        <v>0.5457</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.81335</v>
+        <v>0.51241</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.74378</v>
+        <v>0.45527</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.38</v>
+        <v>1.59</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.625</v>
+        <v>1.0625</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.106</v>
+        <v>0.796</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.625</v>
+        <v>1.0625</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.41</v>
+        <v>0.84</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.4686</v>
+        <v>0.30622</v>
       </c>
       <c r="AO28" t="n">
-        <v>0.4686</v>
+        <v>0.30622</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.93769</v>
+        <v>0.61293</v>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>2501-12-20-FG</t>
+          <t>2501-12-12-FG</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 1/16-12 JIC x 1 1/4-11 1/2 NPTF</t>
+          <t>90 deg Male Elbow, 1 1/16-12 JIC x 3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -5304,59 +5304,59 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED-CORE</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-12-20 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N687 M 1 Size = 1.97 (table had empty); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P687 L 1 Size = 2.38 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R687 Hex Flat = 1.625 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S687 Side 1 ID = 0.609 (table had empty); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X687 Side 2 ID = 1.250 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p23 2501-FG (same source as OMi, not a second source); JIC end: MS33656J chain per dash (gen_straight2 JIC[12], 2403 table, = Brennan, VERIFIED) incl. THDMAJ_A 1.0625; NPTF end: ASME B1.20.3 (ms51500.NPTF[20]) incl. PIPEOD 1.66; end threads from the part number dashes (= catalog B1 / A2 callouts); dims NOT taken from the non-FG Air-Way twin 2501-12-20 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-12-20 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p23 2501-FG on all five body values, same source), not from the non-FG twin 2501-12-20 | leg 2: male NPTF thread dia at L2 1.6709 vs hex flats 1.6250 (round end proud of the flats by 0.0229; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0625 (round end flush with the flats by 0.0018; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>2501-12-20-FG</t>
+          <t>2501-12-12-FG</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2501-16-08-FG</t>
+          <t>2501-12-16-FG</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="C29" t="n">
-        <v>0.65625</v>
+        <v>0.655</v>
       </c>
       <c r="D29" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="E29" t="n">
         <v>0.125</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="J29" t="n">
         <v>60</v>
@@ -5365,43 +5365,43 @@
         <v>37</v>
       </c>
       <c r="L29" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="M29" t="n">
-        <v>0.65625</v>
+        <v>0.655</v>
       </c>
       <c r="N29" t="n">
-        <v>0.40779</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>0.5337</v>
+        <v>0.6828</v>
       </c>
       <c r="P29" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.2163</v>
+        <v>0.2572</v>
       </c>
       <c r="R29" t="n">
-        <v>0.844</v>
+        <v>0.61</v>
       </c>
       <c r="S29" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="T29" t="n">
-        <v>0.531</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="U29" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="V29" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="W29" t="n">
         <v>0.08333</v>
       </c>
       <c r="X29" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="Y29" t="n">
         <v>0.04511</v>
@@ -5413,58 +5413,58 @@
         <v>0.08333</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.81557</v>
+        <v>1.2832</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.5337</v>
+        <v>0.6828</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.08696</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.40779</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.35064</v>
+        <v>0.57203</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.3125</v>
+        <v>1.31</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.899</v>
+        <v>0.896</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.3125</v>
+        <v>1.31</v>
       </c>
       <c r="AK29" t="n">
         <v>1.03</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.65625</v>
+        <v>0.655</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.65625</v>
+        <v>0.655</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.37839</v>
+        <v>0.37766</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.37839</v>
+        <v>0.37766</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.75727</v>
+        <v>0.75583</v>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>2501-16-08-FG</t>
+          <t>2501-12-16-FG</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 5/16-12 JIC x 1/2-14 NPTF</t>
+          <t>90 deg Male Elbow, 1 1/16-12 JIC x 1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -5474,64 +5474,64 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>1 5/16-12 JIC</t>
+          <t>1 1/16-12 JIC</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED-CORE</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-16-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N688 M 1 Size = 1.81 (table had empty); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P688 L 1 Size = 1.78 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R688 Hex Flat = 1.312 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S688 Side 1 ID = 0.844 (table had empty); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X688 Side 2 ID = 0.531 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p23 2501-FG (same source as OMi, not a second source); JIC end: MS33656J chain per dash (gen_straight2 JIC[16], 2403 table, = Brennan, VERIFIED) incl. THDMAJ_A 1.3125; NPTF end: ASME B1.20.3 (ms51500.NPTF[8]) incl. PIPEOD 0.84; end threads from the part number dashes (= catalog B1 / A2 callouts); dims NOT taken from the non-FG Air-Way twin 2501-16-08 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-16-08 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p23 2501-FG on all five body values, same source), not from the non-FG twin 2501-16-08 | hex A/F raised from Air-Way 1.312 to 1.3125 (JIC thread major; 2603HX rule)</t>
+          <t>leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>2501-16-08-FG</t>
+          <t>2501-12-16-FG</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2501-16-12-FG</t>
+          <t>2501-12-20-FG</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="C30" t="n">
-        <v>0.65625</v>
+        <v>0.8125</v>
       </c>
       <c r="D30" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="E30" t="n">
         <v>0.125</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="J30" t="n">
         <v>60</v>
@@ -5540,43 +5540,43 @@
         <v>37</v>
       </c>
       <c r="L30" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="M30" t="n">
-        <v>0.65625</v>
+        <v>0.8125</v>
       </c>
       <c r="N30" t="n">
-        <v>0.51241</v>
+        <v>0.81335</v>
       </c>
       <c r="O30" t="n">
-        <v>0.5457</v>
+        <v>0.7068</v>
       </c>
       <c r="P30" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.2043</v>
+        <v>0.2632</v>
       </c>
       <c r="R30" t="n">
-        <v>0.84</v>
+        <v>0.609</v>
       </c>
       <c r="S30" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="T30" t="n">
-        <v>0.72</v>
+        <v>1.25</v>
       </c>
       <c r="U30" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="W30" t="n">
         <v>0.08333</v>
       </c>
       <c r="X30" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="Y30" t="n">
         <v>0.04511</v>
@@ -5588,58 +5588,58 @@
         <v>0.08333</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.02482</v>
+        <v>1.6267</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.5457</v>
+        <v>0.7068</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.08696</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.51241</v>
+        <v>0.81335</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.45527</v>
+        <v>0.74378</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.3125</v>
+        <v>1.625</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.899</v>
+        <v>1.106</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.3125</v>
+        <v>1.625</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.65625</v>
+        <v>0.8125</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.65625</v>
+        <v>0.8125</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.37839</v>
+        <v>0.4686</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.37839</v>
+        <v>0.4686</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.75727</v>
+        <v>0.93769</v>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>2501-16-12-FG</t>
+          <t>2501-12-20-FG</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 5/16-12 JIC x 3/4-14 NPTF</t>
+          <t>90 deg Male Elbow, 1 1/16-12 JIC x 1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -5649,39 +5649,39 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>1 5/16-12 JIC</t>
+          <t>1 1/16-12 JIC</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>VERIFIED-CORE</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-12-20 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N687 M 1 Size = 1.97 (table had empty); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P687 L 1 Size = 2.38 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R687 Hex Flat = 1.625 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S687 Side 1 ID = 0.609 (table had empty); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X687 Side 2 ID = 1.250 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p23 2501-FG (same source as OMi, not a second source); JIC end: MS33656J chain per dash (gen_straight2 JIC[12], 2403 table, = Brennan, VERIFIED) incl. THDMAJ_A 1.0625; NPTF end: ASME B1.20.3 (ms51500.NPTF[20]) incl. PIPEOD 1.66; end threads from the part number dashes (= catalog B1 / A2 callouts); dims NOT taken from the non-FG Air-Way twin 2501-12-20 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-12-20 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p23 2501-FG on all five body values, same source), not from the non-FG twin 2501-12-20 | leg 2: male NPTF thread dia at L2 1.6709 vs hex flats 1.6250 (round end proud of the flats by 0.0229; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>2501-16-12-FG</t>
+          <t>2501-12-20-FG</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2501-16-16-FG</t>
+          <t>2501-16-08-FG</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -5715,34 +5715,34 @@
         <v>37</v>
       </c>
       <c r="L31" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="M31" t="n">
         <v>0.65625</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.40779</v>
       </c>
       <c r="O31" t="n">
-        <v>0.6828</v>
+        <v>0.5337</v>
       </c>
       <c r="P31" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.2572</v>
+        <v>0.2163</v>
       </c>
       <c r="R31" t="n">
-        <v>0.84</v>
+        <v>0.844</v>
       </c>
       <c r="S31" t="n">
         <v>1.81</v>
       </c>
       <c r="T31" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.531</v>
       </c>
       <c r="U31" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="V31" t="n">
         <v>1.3125</v>
@@ -5763,22 +5763,22 @@
         <v>0.08333</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.2832</v>
+        <v>0.81557</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.6828</v>
+        <v>0.5337</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.40779</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.57203</v>
+        <v>0.35064</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AH31" t="n">
         <v>1.3125</v>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>2501-16-16-FG</t>
+          <t>2501-16-08-FG</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 5/16-12 JIC x 1-11 1/2 NPTF</t>
+          <t>90 deg Male Elbow, 1 5/16-12 JIC x 1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -5829,41 +5829,41 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>VERIFIED-CORE</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-16-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N688 M 1 Size = 1.81 (table had empty); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P688 L 1 Size = 1.78 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R688 Hex Flat = 1.312 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S688 Side 1 ID = 0.844 (table had empty); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X688 Side 2 ID = 0.531 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p23 2501-FG (same source as OMi, not a second source); JIC end: MS33656J chain per dash (gen_straight2 JIC[16], 2403 table, = Brennan, VERIFIED) incl. THDMAJ_A 1.3125; NPTF end: ASME B1.20.3 (ms51500.NPTF[8]) incl. PIPEOD 0.84; end threads from the part number dashes (= catalog B1 / A2 callouts); dims NOT taken from the non-FG Air-Way twin 2501-16-08 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3125 (round end proud of the flats by 0.0067; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-16-08 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p23 2501-FG on all five body values, same source), not from the non-FG twin 2501-16-08 | hex A/F raised from Air-Way 1.312 to 1.3125 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>2501-16-16-FG</t>
+          <t>2501-16-08-FG</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2501-16-20-FG</t>
+          <t>2501-16-12-FG</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="D32" t="n">
         <v>0.65625</v>
@@ -5890,34 +5890,34 @@
         <v>37</v>
       </c>
       <c r="L32" t="n">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="N32" t="n">
-        <v>0.81335</v>
+        <v>0.51241</v>
       </c>
       <c r="O32" t="n">
-        <v>0.7068</v>
+        <v>0.5457</v>
       </c>
       <c r="P32" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.2632</v>
+        <v>0.2043</v>
       </c>
       <c r="R32" t="n">
         <v>0.84</v>
       </c>
       <c r="S32" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="T32" t="n">
-        <v>1.25</v>
+        <v>0.72</v>
       </c>
       <c r="U32" t="n">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="V32" t="n">
         <v>1.3125</v>
@@ -5938,58 +5938,58 @@
         <v>0.08333</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.6267</v>
+        <v>1.02482</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.7068</v>
+        <v>0.5457</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.81335</v>
+        <v>0.51241</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.74378</v>
+        <v>0.45527</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.63</v>
+        <v>1.3125</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.099</v>
+        <v>0.899</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.63</v>
+        <v>1.3125</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.41</v>
+        <v>1.03</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.47004</v>
+        <v>0.37839</v>
       </c>
       <c r="AO32" t="n">
-        <v>0.47004</v>
+        <v>0.37839</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.94058</v>
+        <v>0.75727</v>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>2501-16-20-FG</t>
+          <t>2501-16-12-FG</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 5/16-12 JIC x 1 1/4-11 1/2 NPTF</t>
+          <t>90 deg Male Elbow, 1 5/16-12 JIC x 3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -6019,26 +6019,26 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>leg 2: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>2501-16-20-FG</t>
+          <t>2501-16-12-FG</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2501-16-24-FG</t>
+          <t>2501-16-16-FG</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="D33" t="n">
         <v>0.65625</v>
@@ -6065,34 +6065,34 @@
         <v>37</v>
       </c>
       <c r="L33" t="n">
-        <v>2.64</v>
+        <v>1.97</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="N33" t="n">
-        <v>0.93283</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>0.7235</v>
+        <v>0.6828</v>
       </c>
       <c r="P33" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.2765</v>
+        <v>0.2572</v>
       </c>
       <c r="R33" t="n">
-        <v>0.844</v>
+        <v>0.84</v>
       </c>
       <c r="S33" t="n">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="T33" t="n">
-        <v>1.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="U33" t="n">
-        <v>2.64</v>
+        <v>1.97</v>
       </c>
       <c r="V33" t="n">
         <v>1.3125</v>
@@ -6113,58 +6113,58 @@
         <v>0.08333</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.86566</v>
+        <v>1.2832</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.7235</v>
+        <v>0.6828</v>
       </c>
       <c r="AD33" t="n">
         <v>0.08696</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.93283</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.86326</v>
+        <v>0.57203</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.64</v>
+        <v>1.97</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.875</v>
+        <v>1.3125</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.249</v>
+        <v>0.899</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.875</v>
+        <v>1.3125</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.64</v>
+        <v>1.03</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.54077</v>
+        <v>0.37839</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.54077</v>
+        <v>0.37839</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.08203</v>
+        <v>0.75727</v>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>2501-16-24-FG</t>
+          <t>2501-16-16-FG</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 5/16-12 JIC x 1 1/2-11 1/2 NPTF</t>
+          <t>90 deg Male Elbow, 1 5/16-12 JIC x 1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -6179,59 +6179,59 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED-CORE</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-16-24 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N692 M 1 Size = 2.16 (table had empty); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P692 L 1 Size = 2.64 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R692 Hex Flat = 1.875 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S692 Side 1 ID = 0.844 (table had empty); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X692 Side 2 ID = 1.500 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p23 2501-FG (same source as OMi, not a second source); JIC end: MS33656J chain per dash (gen_straight2 JIC[16], 2403 table, = Brennan, VERIFIED) incl. THDMAJ_A 1.3125; NPTF end: ASME B1.20.3 (ms51500.NPTF[24]) incl. PIPEOD 1.9; end threads from the part number dashes (= catalog B1 / A2 callouts); dims NOT taken from the non-FG Air-Way twin 2501-16-24 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-16-24 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p23 2501-FG on all five body values, same source), not from the non-FG twin 2501-16-24 | leg 2: male NPTF thread dia at L2 1.9109 vs hex flats 1.8750 (round end proud of the flats by 0.0179; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3125 (round end proud of the flats by 0.0067; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>2501-16-24-FG</t>
+          <t>2501-16-16-FG</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2501-20-16-FG</t>
+          <t>2501-16-20-FG</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="C34" t="n">
         <v>0.8149999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="E34" t="n">
         <v>0.125</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="G34" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="J34" t="n">
         <v>60</v>
@@ -6240,43 +6240,43 @@
         <v>37</v>
       </c>
       <c r="L34" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="M34" t="n">
         <v>0.8149999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.81335</v>
       </c>
       <c r="O34" t="n">
-        <v>0.6828</v>
+        <v>0.7068</v>
       </c>
       <c r="P34" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.2572</v>
+        <v>0.2632</v>
       </c>
       <c r="R34" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="S34" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="T34" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="U34" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="V34" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="W34" t="n">
         <v>0.08333</v>
       </c>
       <c r="X34" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="Y34" t="n">
         <v>0.04511</v>
@@ -6288,28 +6288,28 @@
         <v>0.08333</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.2832</v>
+        <v>1.6267</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.6828</v>
+        <v>0.7068</v>
       </c>
       <c r="AD34" t="n">
         <v>0.08696</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.81335</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.57203</v>
+        <v>0.74378</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH34" t="n">
         <v>1.63</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.102</v>
+        <v>1.099</v>
       </c>
       <c r="AJ34" t="n">
         <v>1.63</v>
@@ -6334,12 +6334,12 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>2501-20-16-FG</t>
+          <t>2501-16-20-FG</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 5/8-12 JIC x 1-11 1/2 NPTF</t>
+          <t>90 deg Male Elbow, 1 5/16-12 JIC x 1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>1 5/8-12 JIC</t>
+          <t>1 5/16-12 JIC</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -6367,41 +6367,46 @@
           <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>leg 2: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>2501-20-16-FG</t>
+          <t>2501-16-20-FG</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2501-20-20-FG</t>
+          <t>2501-16-24-FG</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.9375</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="E35" t="n">
         <v>0.125</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="G35" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="J35" t="n">
         <v>60</v>
@@ -6410,43 +6415,43 @@
         <v>37</v>
       </c>
       <c r="L35" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.9375</v>
       </c>
       <c r="N35" t="n">
-        <v>0.81335</v>
+        <v>0.93283</v>
       </c>
       <c r="O35" t="n">
-        <v>0.7068</v>
+        <v>0.7235</v>
       </c>
       <c r="P35" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.2632</v>
+        <v>0.2765</v>
       </c>
       <c r="R35" t="n">
-        <v>1.08</v>
+        <v>0.844</v>
       </c>
       <c r="S35" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="T35" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="U35" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="V35" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="W35" t="n">
         <v>0.08333</v>
       </c>
       <c r="X35" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="Y35" t="n">
         <v>0.04511</v>
@@ -6458,58 +6463,58 @@
         <v>0.08333</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.6267</v>
+        <v>1.86566</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.7068</v>
+        <v>0.7235</v>
       </c>
       <c r="AD35" t="n">
         <v>0.08696</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.81335</v>
+        <v>0.93283</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.74378</v>
+        <v>0.86326</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.63</v>
+        <v>1.875</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.102</v>
+        <v>1.249</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.63</v>
+        <v>1.875</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.9375</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.9375</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.47004</v>
+        <v>0.54077</v>
       </c>
       <c r="AO35" t="n">
-        <v>0.47004</v>
+        <v>0.54077</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.94058</v>
+        <v>1.08203</v>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>2501-20-20-FG</t>
+          <t>2501-16-24-FG</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 5/8-12 JIC x 1 1/4-11 1/2 NPTF</t>
+          <t>90 deg Male Elbow, 1 5/16-12 JIC x 1 1/2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
@@ -6519,46 +6524,46 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>1 5/8-12 JIC</t>
+          <t>1 5/16-12 JIC</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>1 1/2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>VERIFIED-CORE</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-16-24 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N692 M 1 Size = 2.16 (table had empty); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P692 L 1 Size = 2.64 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R692 Hex Flat = 1.875 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S692 Side 1 ID = 0.844 (table had empty); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X692 Side 2 ID = 1.500 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p23 2501-FG (same source as OMi, not a second source); JIC end: MS33656J chain per dash (gen_straight2 JIC[16], 2403 table, = Brennan, VERIFIED) incl. THDMAJ_A 1.3125; NPTF end: ASME B1.20.3 (ms51500.NPTF[24]) incl. PIPEOD 1.9; end threads from the part number dashes (= catalog B1 / A2 callouts); dims NOT taken from the non-FG Air-Way twin 2501-16-24 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>leg 2: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-16-24 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p23 2501-FG on all five body values, same source), not from the non-FG twin 2501-16-24 | leg 2: male NPTF thread dia at L2 1.9109 vs hex flats 1.8750 (round end proud of the flats by 0.0179; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>2501-20-20-FG</t>
+          <t>2501-16-24-FG</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2501-20-24-FG</t>
+          <t>2501-20-16-FG</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="D36" t="n">
         <v>0.8125</v>
@@ -6585,34 +6590,34 @@
         <v>37</v>
       </c>
       <c r="L36" t="n">
-        <v>2.64</v>
+        <v>2.35</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>0.93283</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>0.7235</v>
+        <v>0.6828</v>
       </c>
       <c r="P36" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2765</v>
+        <v>0.2572</v>
       </c>
       <c r="R36" t="n">
         <v>1.08</v>
       </c>
       <c r="S36" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="T36" t="n">
-        <v>1.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="U36" t="n">
-        <v>2.64</v>
+        <v>2.35</v>
       </c>
       <c r="V36" t="n">
         <v>1.625</v>
@@ -6633,58 +6638,58 @@
         <v>0.08333</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.86566</v>
+        <v>1.2832</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.7235</v>
+        <v>0.6828</v>
       </c>
       <c r="AD36" t="n">
         <v>0.08696</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.93283</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.86326</v>
+        <v>0.57203</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.64</v>
+        <v>2.35</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.342</v>
+        <v>1.102</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AN36" t="n">
-        <v>0.54221</v>
+        <v>0.47004</v>
       </c>
       <c r="AO36" t="n">
-        <v>0.54221</v>
+        <v>0.47004</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.08492</v>
+        <v>0.94058</v>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>2501-20-24-FG</t>
+          <t>2501-20-16-FG</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 5/8-12 JIC x 1 1/2-11 1/2 NPTF</t>
+          <t>90 deg Male Elbow, 1 5/8-12 JIC x 1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
@@ -6699,7 +6704,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -6712,46 +6717,41 @@
           <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>leg 2: male NPTF thread dia at L2 1.9109 vs hex flats 1.8800 (round end proud of the flats by 0.0154; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
-        </is>
-      </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>2501-20-24-FG</t>
+          <t>2501-20-16-FG</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2501-24-16-FG</t>
+          <t>2501-20-20-FG</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9375</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="E37" t="n">
         <v>0.125</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="J37" t="n">
         <v>60</v>
@@ -6760,43 +6760,43 @@
         <v>37</v>
       </c>
       <c r="L37" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="M37" t="n">
-        <v>0.9375</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.81335</v>
       </c>
       <c r="O37" t="n">
-        <v>0.6828</v>
+        <v>0.7068</v>
       </c>
       <c r="P37" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.2572</v>
+        <v>0.2632</v>
       </c>
       <c r="R37" t="n">
-        <v>1.312</v>
+        <v>1.08</v>
       </c>
       <c r="S37" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="T37" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="U37" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="V37" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="W37" t="n">
         <v>0.08333</v>
       </c>
       <c r="X37" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="Y37" t="n">
         <v>0.04511</v>
@@ -6808,58 +6808,58 @@
         <v>0.08333</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.2832</v>
+        <v>1.6267</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.6828</v>
+        <v>0.7068</v>
       </c>
       <c r="AD37" t="n">
         <v>0.08696</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.81335</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.57203</v>
+        <v>0.74378</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.875</v>
+        <v>1.63</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.247</v>
+        <v>1.102</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.875</v>
+        <v>1.63</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.9375</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.9375</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.54077</v>
+        <v>0.47004</v>
       </c>
       <c r="AO37" t="n">
-        <v>0.54077</v>
+        <v>0.47004</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.08203</v>
+        <v>0.94058</v>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>2501-24-16-FG</t>
+          <t>2501-20-20-FG</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 7/8-12 JIC x 1-11 1/2 NPTF</t>
+          <t>90 deg Male Elbow, 1 5/8-12 JIC x 1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
@@ -6869,64 +6869,64 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>1 7/8-12 JIC</t>
+          <t>1 5/8-12 JIC</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED-CORE</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-24-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N696 M 1 Size = 2.33 (table had empty); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P696 L 1 Size = 2.58 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R696 Hex Flat = 1.875 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S696 Side 1 ID = 1.312 (table had empty); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X696 Side 2 ID = 0.938 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p23 2501-FG (same source as OMi, not a second source); JIC end: MS33656J chain per dash (gen_straight2 JIC[24], 2403 table, = Brennan, VERIFIED) incl. THDMAJ_A 1.875; NPTF end: ASME B1.20.3 (ms51500.NPTF[16]) incl. PIPEOD 1.315; end threads from the part number dashes (= catalog B1 / A2 callouts); dims NOT taken from the non-FG Air-Way twin 2501-24-16 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-24-16 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p23 2501-FG on all five body values, same source), not from the non-FG twin 2501-24-16</t>
+          <t>leg 2: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>2501-24-16-FG</t>
+          <t>2501-20-20-FG</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2501-24-20-FG</t>
+          <t>2501-20-24-FG</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="C38" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="E38" t="n">
         <v>0.125</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="J38" t="n">
         <v>60</v>
@@ -6935,43 +6935,43 @@
         <v>37</v>
       </c>
       <c r="L38" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="M38" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>0.81335</v>
+        <v>0.93283</v>
       </c>
       <c r="O38" t="n">
-        <v>0.7068</v>
+        <v>0.7235</v>
       </c>
       <c r="P38" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.2632</v>
+        <v>0.2765</v>
       </c>
       <c r="R38" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="S38" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="T38" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="U38" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="V38" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="W38" t="n">
         <v>0.08333</v>
       </c>
       <c r="X38" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="Y38" t="n">
         <v>0.04511</v>
@@ -6983,28 +6983,28 @@
         <v>0.08333</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.6267</v>
+        <v>1.86566</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.7068</v>
+        <v>0.7235</v>
       </c>
       <c r="AD38" t="n">
         <v>0.08696</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.81335</v>
+        <v>0.93283</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.74378</v>
+        <v>0.86326</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="AH38" t="n">
         <v>1.88</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.247</v>
+        <v>1.242</v>
       </c>
       <c r="AJ38" t="n">
         <v>1.88</v>
@@ -7029,12 +7029,12 @@
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>2501-24-20-FG</t>
+          <t>2501-20-24-FG</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 7/8-12 JIC x 1 1/4-11 1/2 NPTF</t>
+          <t>90 deg Male Elbow, 1 5/8-12 JIC x 1 1/2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>1 7/8-12 JIC</t>
+          <t>1 5/8-12 JIC</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>1 1/2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -7059,19 +7059,24 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504); M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N695 = 2.20 (table had 2.3) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): M@DRIVE 2.3 -&gt; OMi 2.20 (Items!N695, M071) | leg 2: male NPTF thread dia at L2 1.9109 vs hex flats 1.8800 (round end proud of the flats by 0.0154; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>2501-24-20-FG</t>
+          <t>2501-20-24-FG</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2501-24-24-FG</t>
+          <t>2501-24-16-FG</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -7105,34 +7110,34 @@
         <v>37</v>
       </c>
       <c r="L39" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="M39" t="n">
         <v>0.9375</v>
       </c>
       <c r="N39" t="n">
-        <v>0.93283</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>0.7235</v>
+        <v>0.6828</v>
       </c>
       <c r="P39" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.2765</v>
+        <v>0.2572</v>
       </c>
       <c r="R39" t="n">
-        <v>1.31</v>
+        <v>1.312</v>
       </c>
       <c r="S39" t="n">
         <v>2.33</v>
       </c>
       <c r="T39" t="n">
-        <v>1.5</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="U39" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="V39" t="n">
         <v>1.875</v>
@@ -7153,22 +7158,22 @@
         <v>0.08333</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.86566</v>
+        <v>1.2832</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.7235</v>
+        <v>0.6828</v>
       </c>
       <c r="AD39" t="n">
         <v>0.08696</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.93283</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.86326</v>
+        <v>0.57203</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AH39" t="n">
         <v>1.875</v>
@@ -7199,12 +7204,12 @@
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>2501-24-24-FG</t>
+          <t>2501-24-16-FG</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 7/8-12 JIC x 1 1/2-11 1/2 NPTF</t>
+          <t>90 deg Male Elbow, 1 7/8-12 JIC x 1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -7219,7 +7224,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -7229,31 +7234,31 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R698 Hex Flat = 1.875 (table had 1.81) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-24-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N696 M 1 Size = 2.33 (table had empty); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P696 L 1 Size = 2.58 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R696 Hex Flat = 1.875 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S696 Side 1 ID = 1.312 (table had empty); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X696 Side 2 ID = 0.938 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p23 2501-FG (same source as OMi, not a second source); JIC end: MS33656J chain per dash (gen_straight2 JIC[24], 2403 table, = Brennan, VERIFIED) incl. THDMAJ_A 1.875; NPTF end: ASME B1.20.3 (ms51500.NPTF[16]) incl. PIPEOD 1.315; end threads from the part number dashes (= catalog B1 / A2 callouts); dims NOT taken from the non-FG Air-Way twin 2501-24-16 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>leg 2: male NPTF thread dia at L2 1.9109 vs hex flats 1.8750 (round end proud of the flats by 0.0179; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-24-16 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p23 2501-FG on all five body values, same source), not from the non-FG twin 2501-24-16</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>2501-24-24-FG</t>
+          <t>2501-24-16-FG</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2501-24-32-FG</t>
+          <t>2501-24-20-FG</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.81</v>
+        <v>2.33</v>
       </c>
       <c r="C40" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D40" t="n">
         <v>0.9375</v>
@@ -7280,34 +7285,34 @@
         <v>37</v>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="M40" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="O40" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="P40" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.2735</v>
+        <v>0.2632</v>
       </c>
       <c r="R40" t="n">
-        <v>1.312</v>
+        <v>1.31</v>
       </c>
       <c r="S40" t="n">
-        <v>2.81</v>
+        <v>2.33</v>
       </c>
       <c r="T40" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="U40" t="n">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="V40" t="n">
         <v>1.875</v>
@@ -7328,58 +7333,58 @@
         <v>0.08333</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.33859</v>
+        <v>1.6267</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="AD40" t="n">
         <v>0.08696</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.09973</v>
+        <v>0.74378</v>
       </c>
       <c r="AG40" t="n">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.727</v>
+        <v>1.247</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AN40" t="n">
-        <v>0.72119</v>
+        <v>0.54221</v>
       </c>
       <c r="AO40" t="n">
-        <v>0.72119</v>
+        <v>0.54221</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.44288</v>
+        <v>1.08492</v>
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>2501-24-32-FG</t>
+          <t>2501-24-20-FG</t>
         </is>
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 7/8-12 JIC x 2-11 1/2 NPTF</t>
+          <t>90 deg Male Elbow, 1 7/8-12 JIC x 1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -7394,59 +7399,54 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2-11 1/2 NPTF</t>
+          <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED-CORE</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N699 M 1 Size = 2.81 (table had empty); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P699 L 1 Size = 3.00 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R699 Hex Flat = 2.500 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S699 Side 1 ID = 1.312 (table had empty); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X699 Side 2 ID = 1.940 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F2a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p23 2501-FG (same source as OMi, not a second source) except D1 (catalog 1.938); JIC end: MS33656J chain per dash (gen_straight2 JIC[24], 2403 table, = Brennan, VERIFIED) incl. THDMAJ_A 1.875; NPTF end: ASME B1.20.3 (ms51500.NPTF[32]) incl. PIPEOD 2.375; end threads from the part number dashes (= catalog B1 / A2 callouts) [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | RESOLVED 2026-10-02 (batch 15, staged): dimensions from OMi (one source, ASSUMED; the Brennan catalog TFA p23 is the same source); D1@DRILL: OMi Side 2 ID 1.940 (Items!X699) vs Brennan TFA p23 A2 DRILL 1.938 (= 1-15/16; OMi's own 2501-32-32-FG prints 1.938) - OMi kept by the OMi-first rule, open question Q-NEW-F2A-OMIvsCAT (no build depends on it)</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>2501-24-32-FG</t>
+          <t>2501-24-20-FG</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2501-32-24-FG</t>
+          <t>2501-24-24-FG</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.06</v>
+        <v>2.33</v>
       </c>
       <c r="C41" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="D41" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="E41" t="n">
         <v>0.125</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="G41" t="n">
-        <v>1.19</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1292</v>
+        <v>0.1298</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3318</v>
+        <v>0.2482</v>
       </c>
       <c r="J41" t="n">
         <v>60</v>
@@ -7455,10 +7455,10 @@
         <v>37</v>
       </c>
       <c r="L41" t="n">
-        <v>2.97</v>
+        <v>2.64</v>
       </c>
       <c r="M41" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="N41" t="n">
         <v>0.93283</v>
@@ -7473,25 +7473,25 @@
         <v>0.2765</v>
       </c>
       <c r="R41" t="n">
-        <v>1.78</v>
+        <v>1.31</v>
       </c>
       <c r="S41" t="n">
-        <v>3.06</v>
+        <v>2.33</v>
       </c>
       <c r="T41" t="n">
         <v>1.5</v>
       </c>
       <c r="U41" t="n">
-        <v>2.97</v>
+        <v>2.64</v>
       </c>
       <c r="V41" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="W41" t="n">
         <v>0.08333</v>
       </c>
       <c r="X41" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="Y41" t="n">
         <v>0.04511</v>
@@ -7518,43 +7518,43 @@
         <v>0.86326</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.97</v>
+        <v>2.64</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.727</v>
+        <v>1.247</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.72119</v>
+        <v>0.54077</v>
       </c>
       <c r="AO41" t="n">
-        <v>0.72119</v>
+        <v>0.54077</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.44288</v>
+        <v>1.08203</v>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>2501-32-24-FG</t>
+          <t>2501-24-24-FG</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 2 1/2-12 JIC x 1 1/2-11 1/2 NPTF</t>
+          <t>90 deg Male Elbow, 1 7/8-12 JIC x 1 1/2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>2 1/2-12 JIC</t>
+          <t>1 7/8-12 JIC</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
@@ -7574,49 +7574,54 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>VERIFIED-CORE</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R698 Hex Flat = 1.875 (table had 1.81) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>leg 2: male NPTF thread dia at L2 1.9109 vs hex flats 1.8750 (round end proud of the flats by 0.0179; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>2501-32-24-FG</t>
+          <t>2501-24-24-FG</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2501-32-32-FG</t>
+          <t>2501-24-32-FG</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.06</v>
+        <v>2.81</v>
       </c>
       <c r="C42" t="n">
         <v>1.25</v>
       </c>
       <c r="D42" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="E42" t="n">
         <v>0.125</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="G42" t="n">
-        <v>1.19</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1292</v>
+        <v>0.1298</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3318</v>
+        <v>0.2482</v>
       </c>
       <c r="J42" t="n">
         <v>60</v>
@@ -7643,25 +7648,25 @@
         <v>0.2735</v>
       </c>
       <c r="R42" t="n">
-        <v>1.78</v>
+        <v>1.312</v>
       </c>
       <c r="S42" t="n">
-        <v>3.06</v>
+        <v>2.81</v>
       </c>
       <c r="T42" t="n">
-        <v>1.938</v>
+        <v>1.94</v>
       </c>
       <c r="U42" t="n">
         <v>3</v>
       </c>
       <c r="V42" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="W42" t="n">
         <v>0.08333</v>
       </c>
       <c r="X42" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="Y42" t="n">
         <v>0.04511</v>
@@ -7719,12 +7724,12 @@
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>2501-32-32-FG</t>
+          <t>2501-24-32-FG</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 2 1/2-12 JIC x 2-11 1/2 NPTF</t>
+          <t>90 deg Male Elbow, 1 7/8-12 JIC x 2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
@@ -7734,7 +7739,7 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>2 1/2-12 JIC</t>
+          <t>1 7/8-12 JIC</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
@@ -7749,49 +7754,49 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>was "VERIFIED" (vote text in the wrong column); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R701 Hex Flat = 2.500 (table had 1.938, the voted drill shifted into this column); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X701 Side 2 ID = 1.938 (table had 1.86) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; legs/bore/ends as the other 2501 -FG rows (Air-Way legs, JIC end MS33656J = Brennan, NPTF ASME B1.20.3) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N699 M 1 Size = 2.81 (table had empty); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P699 L 1 Size = 3.00 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R699 Hex Flat = 2.500 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S699 Side 1 ID = 1.312 (table had empty); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X699 Side 2 ID = 1.940 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F2a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p23 2501-FG (same source as OMi, not a second source) except D1 (catalog 1.938); JIC end: MS33656J chain per dash (gen_straight2 JIC[24], 2403 table, = Brennan, VERIFIED) incl. THDMAJ_A 1.875; NPTF end: ASME B1.20.3 (ms51500.NPTF[32]) incl. PIPEOD 2.375; end threads from the part number dashes (= catalog B1 / A2 callouts) [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>CONFLICT vs MS51504 - see workbook | 2026-09-25: Air-Way vs MS51504 drill conflict resolved by the OMi-first rule (OMi Side 2 ID 1.938 = MS51504 + Brennan); Y@REF held the voted drill 1.938 (column shift, audit 3.5) - OMi Hex Flat 2.500 = Air-Way printed Y 2.50</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | RESOLVED 2026-10-02 (batch 15, staged): dimensions from OMi (one source, ASSUMED; the Brennan catalog TFA p23 is the same source); D1@DRILL: OMi Side 2 ID 1.940 (Items!X699) vs Brennan TFA p23 A2 DRILL 1.938 (= 1-15/16; OMi's own 2501-32-32-FG prints 1.938) - OMi kept by the OMi-first rule, open question Q-NEW-F2A-OMIvsCAT (no build depends on it)</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>2501-32-32-FG</t>
+          <t>2501-24-32-FG</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2501-L-04-02-FG</t>
+          <t>2501-32-24-FG</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.89</v>
+        <v>3.06</v>
       </c>
       <c r="C43" t="n">
-        <v>0.22</v>
+        <v>1.25</v>
       </c>
       <c r="D43" t="n">
-        <v>0.21875</v>
+        <v>1.25</v>
       </c>
       <c r="E43" t="n">
-        <v>0.075</v>
+        <v>0.125</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2608</v>
+        <v>0.7124</v>
       </c>
       <c r="G43" t="n">
-        <v>0.182</v>
+        <v>1.19</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0795</v>
+        <v>0.1292</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1135</v>
+        <v>0.3318</v>
       </c>
       <c r="J43" t="n">
         <v>60</v>
@@ -7800,106 +7805,106 @@
         <v>37</v>
       </c>
       <c r="L43" t="n">
-        <v>1.19</v>
+        <v>2.97</v>
       </c>
       <c r="M43" t="n">
-        <v>0.22</v>
+        <v>1.25</v>
       </c>
       <c r="N43" t="n">
-        <v>0.19657</v>
+        <v>0.93283</v>
       </c>
       <c r="O43" t="n">
-        <v>0.2639</v>
+        <v>0.7235</v>
       </c>
       <c r="P43" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.1161</v>
+        <v>0.2765</v>
       </c>
       <c r="R43" t="n">
-        <v>0.17</v>
+        <v>1.78</v>
       </c>
       <c r="S43" t="n">
-        <v>0.89</v>
+        <v>3.06</v>
       </c>
       <c r="T43" t="n">
-        <v>0.19</v>
+        <v>1.5</v>
       </c>
       <c r="U43" t="n">
-        <v>1.19</v>
+        <v>2.97</v>
       </c>
       <c r="V43" t="n">
-        <v>0.4375</v>
+        <v>2.5</v>
       </c>
       <c r="W43" t="n">
-        <v>0.05</v>
+        <v>0.08333</v>
       </c>
       <c r="X43" t="n">
-        <v>0.2608</v>
+        <v>0.7124</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.02706</v>
+        <v>0.04511</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.0125</v>
+        <v>0.02083</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.05</v>
+        <v>0.08333</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.39314</v>
+        <v>1.86566</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.2639</v>
+        <v>0.7235</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.03704</v>
+        <v>0.08696</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.19657</v>
+        <v>0.93283</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.16694</v>
+        <v>0.86326</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.19</v>
+        <v>2.97</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.44</v>
+        <v>2.5</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.34</v>
+        <v>1.727</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.44</v>
+        <v>2.5</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.97</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.22</v>
+        <v>1.25</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.22</v>
+        <v>1.25</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.12652</v>
+        <v>0.72119</v>
       </c>
       <c r="AO43" t="n">
-        <v>0.12652</v>
+        <v>0.72119</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.25353</v>
+        <v>1.44288</v>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>2501-L-04-02-FG</t>
+          <t>2501-32-24-FG</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 7/16-20 JIC x 1/8-27 NPTF</t>
+          <t>90 deg Male Elbow, 2 1/2-12 JIC x 1 1/2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -7909,64 +7914,59 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>7/16-20 JIC</t>
+          <t>2 1/2-12 JIC</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>1/8-27 NPTF</t>
+          <t>1 1/2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>VERIFIED-LEGS</t>
+          <t>VERIFIED-CORE</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Air-Way s119 only (double-pass 21 rows); M leg matches verified 2501 family; N3 long leg single-source; JIC end VERIFIED (MS33656J) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>M matches verified 2501 M family | 2501L row folded into the 2501 master (user decision 2026-09-25)</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>2501-L-04-02-FG</t>
+          <t>2501-32-24-FG</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2501-L-04-04-FG</t>
+          <t>2501-32-32-FG</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.05</v>
+        <v>3.06</v>
       </c>
       <c r="C44" t="n">
-        <v>0.281</v>
+        <v>1.25</v>
       </c>
       <c r="D44" t="n">
-        <v>0.21875</v>
+        <v>1.25</v>
       </c>
       <c r="E44" t="n">
-        <v>0.075</v>
+        <v>0.125</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2608</v>
+        <v>0.7124</v>
       </c>
       <c r="G44" t="n">
-        <v>0.182</v>
+        <v>1.19</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0795</v>
+        <v>0.1292</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1135</v>
+        <v>0.3318</v>
       </c>
       <c r="J44" t="n">
         <v>60</v>
@@ -7975,106 +7975,106 @@
         <v>37</v>
       </c>
       <c r="L44" t="n">
-        <v>1.58</v>
+        <v>3</v>
       </c>
       <c r="M44" t="n">
-        <v>0.281</v>
+        <v>1.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0.26092</v>
+        <v>1.16929</v>
       </c>
       <c r="O44" t="n">
-        <v>0.4018</v>
+        <v>0.7565</v>
       </c>
       <c r="P44" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.1582</v>
+        <v>0.2735</v>
       </c>
       <c r="R44" t="n">
-        <v>0.172</v>
+        <v>1.78</v>
       </c>
       <c r="S44" t="n">
-        <v>1.05</v>
+        <v>3.06</v>
       </c>
       <c r="T44" t="n">
-        <v>0.281</v>
+        <v>1.938</v>
       </c>
       <c r="U44" t="n">
-        <v>1.58</v>
+        <v>3</v>
       </c>
       <c r="V44" t="n">
-        <v>0.4375</v>
+        <v>2.5</v>
       </c>
       <c r="W44" t="n">
-        <v>0.05</v>
+        <v>0.08333</v>
       </c>
       <c r="X44" t="n">
-        <v>0.2608</v>
+        <v>0.7124</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.02706</v>
+        <v>0.04511</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.0125</v>
+        <v>0.02083</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.05</v>
+        <v>0.08333</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.52183</v>
+        <v>2.33859</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.4018</v>
+        <v>0.7565</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.05556</v>
+        <v>0.08696</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.26092</v>
+        <v>1.16929</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.21647</v>
+        <v>1.09973</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.58</v>
+        <v>3</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.5620000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.5</v>
+        <v>1.727</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.5620000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.02</v>
+        <v>1.97</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.281</v>
+        <v>1.25</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.281</v>
+        <v>1.25</v>
       </c>
       <c r="AN44" t="n">
-        <v>0.16174</v>
+        <v>0.72119</v>
       </c>
       <c r="AO44" t="n">
-        <v>0.16174</v>
+        <v>0.72119</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.32397</v>
+        <v>1.44288</v>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>2501-L-04-04-FG</t>
+          <t>2501-32-32-FG</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 7/16-20 JIC x 1/4-18 NPTF</t>
+          <t>90 deg Male Elbow, 2 1/2-12 JIC x 2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>7/16-20 JIC</t>
+          <t>2 1/2-12 JIC</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF</t>
+          <t>2-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -8099,49 +8099,49 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-L-04-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N704 M 1 Size = 1.050 (table had empty); N3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P704 L 1 Size = 1.580 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R704 Hex Flat = 0.562 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S704 Side 1 ID = 0.172 (table had empty); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!X704 Side 2 ID = 0.281 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N3@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p24 2501-L-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 13/13 (M) and 12/13 (L) rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p24 2501-L-FG (same source as OMi, not a second source); JIC end: MS33656J (gen_straight2 JIC[4], VERIFIED) THDMAJ_B 0.4375; NPTF end ASME B1.20.3 (ms51500.NPTF[4]) THDMAJ_A 0.54; threads from the part number dashes (= catalog callouts); dims NOT taken from the non-FG Air-Way twin 2501-L-04-04 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>was "VERIFIED" (vote text in the wrong column); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R701 Hex Flat = 2.500 (table had 1.938, the voted drill shifted into this column); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X701 Side 2 ID = 1.938 (table had 1.86) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; legs/bore/ends as the other 2501 -FG rows (Air-Way legs, JIC end MS33656J = Brennan, NPTF ASME B1.20.3) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-L-04-04 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p24 2501-L-FG on all five body values, same source), not from the non-FG twin 2501-L-04-04; OMi Items!U704 Side 1 Thread '1-5/8-12 UN' is wrong for a -04 JIC end (catalog B1 7/16-20; the thread follows the part number) - report to OMi (question 29) | 2501L row folded into the 2501 master (user decision 2026-09-25)</t>
+          <t>CONFLICT vs MS51504 - see workbook | 2026-09-25: Air-Way vs MS51504 drill conflict resolved by the OMi-first rule (OMi Side 2 ID 1.938 = MS51504 + Brennan); Y@REF held the voted drill 1.938 (column shift, audit 3.5) - OMi Hex Flat 2.500 = Air-Way printed Y 2.50</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>2501-L-04-04-FG</t>
+          <t>2501-32-32-FG</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2501-L-06-04-FG</t>
+          <t>2501-L-04-02-FG</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="C45" t="n">
-        <v>0.28125</v>
+        <v>0.22</v>
       </c>
       <c r="D45" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="E45" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="J45" t="n">
         <v>60</v>
@@ -8150,106 +8150,106 @@
         <v>37</v>
       </c>
       <c r="L45" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="M45" t="n">
-        <v>0.28125</v>
+        <v>0.22</v>
       </c>
       <c r="N45" t="n">
-        <v>0.26092</v>
+        <v>0.19657</v>
       </c>
       <c r="O45" t="n">
-        <v>0.4018</v>
+        <v>0.2639</v>
       </c>
       <c r="P45" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.1582</v>
+        <v>0.1161</v>
       </c>
       <c r="R45" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="S45" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="T45" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="U45" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="V45" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="W45" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="X45" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.52183</v>
+        <v>0.39314</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.4018</v>
+        <v>0.2639</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.05556</v>
+        <v>0.03704</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.26092</v>
+        <v>0.19657</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.21647</v>
+        <v>0.16694</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.5625</v>
+        <v>0.44</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.504</v>
+        <v>0.34</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.5625</v>
+        <v>0.44</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.28125</v>
+        <v>0.22</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.28125</v>
+        <v>0.22</v>
       </c>
       <c r="AN45" t="n">
-        <v>0.16188</v>
+        <v>0.12652</v>
       </c>
       <c r="AO45" t="n">
-        <v>0.16188</v>
+        <v>0.12652</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.32426</v>
+        <v>0.25353</v>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>2501-L-06-04-FG</t>
+          <t>2501-L-04-02-FG</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 9/16-18 JIC x 1/4-18 NPTF</t>
+          <t>90 deg Male Elbow, 7/16-20 JIC x 1/8-27 NPTF</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>9/16-18 JIC</t>
+          <t>7/16-20 JIC</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF</t>
+          <t>1/8-27 NPTF</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -8274,49 +8274,49 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Air-Way s119 only (double-pass 21 rows); M leg matches verified 2501 family; N3 long leg single-source; JIC end VERIFIED (MS33656J) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s119 only (double-pass 21 rows); M leg matches verified 2501 family; N3 long leg single-source; JIC end VERIFIED (MS33656J); N3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P703 = 1.170 (table had 1.19) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>M matches verified 2501 M family | 2501L row folded into the 2501 master (user decision 2026-09-25) | hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
+          <t>M matches verified 2501 M family | A19 (user 2026-10-18, group 2 settled): N3@DRIVE 1.19 -&gt; OMi 1.170 (Items!P703, M077) | 2501L row folded into the 2501 master (user decision 2026-09-25)</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>2501-L-06-04-FG</t>
+          <t>2501-L-04-02-FG</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2501-L-06-06-FG</t>
+          <t>2501-L-04-04-FG</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="C46" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="D46" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="E46" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="J46" t="n">
         <v>60</v>
@@ -8325,106 +8325,106 @@
         <v>37</v>
       </c>
       <c r="L46" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="M46" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="N46" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="O46" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="P46" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.1522</v>
+        <v>0.1582</v>
       </c>
       <c r="R46" t="n">
-        <v>0.3</v>
+        <v>0.172</v>
       </c>
       <c r="S46" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="T46" t="n">
-        <v>0.41</v>
+        <v>0.281</v>
       </c>
       <c r="U46" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="V46" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="W46" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="X46" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.65645</v>
+        <v>0.52183</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="AD46" t="n">
         <v>0.05556</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.28378</v>
+        <v>0.21647</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.75</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.584</v>
+        <v>0.5</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.75</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="AN46" t="n">
-        <v>0.21601</v>
+        <v>0.16174</v>
       </c>
       <c r="AO46" t="n">
-        <v>0.21601</v>
+        <v>0.16174</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.43251</v>
+        <v>0.32397</v>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>2501-L-06-06-FG</t>
+          <t>2501-L-04-04-FG</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 9/16-18 JIC x 3/8-18 NPTF</t>
+          <t>90 deg Male Elbow, 7/16-20 JIC x 1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>9/16-18 JIC</t>
+          <t>7/16-20 JIC</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF</t>
+          <t>1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -8449,49 +8449,49 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Air-Way s119 only (double-pass 21 rows); M leg matches verified 2501 family; N3 long leg single-source; JIC end VERIFIED (MS33656J) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-L-04-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N704 M 1 Size = 1.050 (table had empty); N3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P704 L 1 Size = 1.580 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R704 Hex Flat = 0.562 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S704 Side 1 ID = 0.172 (table had empty); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!X704 Side 2 ID = 0.281 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N3@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p24 2501-L-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 13/13 (M) and 12/13 (L) rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p24 2501-L-FG (same source as OMi, not a second source); JIC end: MS33656J (gen_straight2 JIC[4], VERIFIED) THDMAJ_B 0.4375; NPTF end ASME B1.20.3 (ms51500.NPTF[4]) THDMAJ_A 0.54; threads from the part number dashes (= catalog callouts); dims NOT taken from the non-FG Air-Way twin 2501-L-04-04 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>2501L row folded into the 2501 master (user decision 2026-09-25)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-L-04-04 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p24 2501-L-FG on all five body values, same source), not from the non-FG twin 2501-L-04-04; OMi Items!U704 Side 1 Thread '1-5/8-12 UN' is wrong for a -04 JIC end (catalog B1 7/16-20; the thread follows the part number) - report to OMi (question 29) | 2501L row folded into the 2501 master (user decision 2026-09-25)</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>2501-L-06-06-FG</t>
+          <t>2501-L-04-04-FG</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2501-L-08-08-FG</t>
+          <t>2501-L-06-04-FG</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="D47" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="E47" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2837</v>
+        <v>0.2515</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3295</v>
+        <v>0.2405</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0984</v>
+        <v>0.0898</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="J47" t="n">
         <v>60</v>
@@ -8500,106 +8500,106 @@
         <v>37</v>
       </c>
       <c r="L47" t="n">
-        <v>2.17</v>
+        <v>1.58</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="N47" t="n">
-        <v>0.40779</v>
+        <v>0.26092</v>
       </c>
       <c r="O47" t="n">
-        <v>0.5337</v>
+        <v>0.4018</v>
       </c>
       <c r="P47" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.2163</v>
+        <v>0.1582</v>
       </c>
       <c r="R47" t="n">
-        <v>0.391</v>
+        <v>0.3</v>
       </c>
       <c r="S47" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="T47" t="n">
-        <v>0.531</v>
+        <v>0.28</v>
       </c>
       <c r="U47" t="n">
-        <v>2.17</v>
+        <v>1.58</v>
       </c>
       <c r="V47" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="W47" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="X47" t="n">
-        <v>0.2837</v>
+        <v>0.2515</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.81557</v>
+        <v>0.52183</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.5337</v>
+        <v>0.4018</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.40779</v>
+        <v>0.26092</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.35064</v>
+        <v>0.21647</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.17</v>
+        <v>1.58</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.875</v>
+        <v>0.5625</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.673</v>
+        <v>0.504</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.875</v>
+        <v>0.5625</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="AN47" t="n">
-        <v>0.25209</v>
+        <v>0.16188</v>
       </c>
       <c r="AO47" t="n">
-        <v>0.25209</v>
+        <v>0.16188</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.50468</v>
+        <v>0.32426</v>
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>2501-L-08-08-FG</t>
+          <t>2501-L-06-04-FG</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 3/4-16 JIC x 1/2-14 NPTF</t>
+          <t>90 deg Male Elbow, 9/16-18 JIC x 1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
@@ -8609,64 +8609,64 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>3/4-16 JIC</t>
+          <t>9/16-18 JIC</t>
         </is>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED-LEGS</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-L-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N708 M 1 Size = 1.330 (table had empty); N3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P708 L 1 Size = 2.170 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R708 Hex Flat = 0.875 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S708 Side 1 ID = 0.391 (table had empty); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!X708 Side 2 ID = 0.531 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N3@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p24 2501-L-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 13/13 (M) and 12/13 (L) rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p24 2501-L-FG (same source as OMi, not a second source); JIC end: MS33656J (gen_straight2 JIC[8], VERIFIED) THDMAJ_B 0.75; NPTF end ASME B1.20.3 (ms51500.NPTF[8]) THDMAJ_A 0.84; threads from the part number dashes (= catalog callouts); dims NOT taken from the non-FG Air-Way twin 2501-L-08-08 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s119 only (double-pass 21 rows); M leg matches verified 2501 family; N3 long leg single-source; JIC end VERIFIED (MS33656J) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-L-08-08 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p24 2501-L-FG on all five body values, same source), not from the non-FG twin 2501-L-08-08 | 2501L row folded into the 2501 master (user decision 2026-09-25)</t>
+          <t>M matches verified 2501 M family | 2501L row folded into the 2501 master (user decision 2026-09-25) | hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>2501-L-08-08-FG</t>
+          <t>2501-L-06-04-FG</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2501-L-12-12-FG</t>
+          <t>2501-L-06-06-FG</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="C48" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="D48" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="E48" t="n">
-        <v>0.125</v>
+        <v>0.083</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3895</v>
+        <v>0.2515</v>
       </c>
       <c r="G48" t="n">
-        <v>0.4715</v>
+        <v>0.2405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1299</v>
+        <v>0.0898</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1851</v>
+        <v>0.1082</v>
       </c>
       <c r="J48" t="n">
         <v>60</v>
@@ -8675,106 +8675,106 @@
         <v>37</v>
       </c>
       <c r="L48" t="n">
-        <v>2.44</v>
+        <v>1.82</v>
       </c>
       <c r="M48" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="N48" t="n">
-        <v>0.51241</v>
+        <v>0.32823</v>
       </c>
       <c r="O48" t="n">
-        <v>0.5457</v>
+        <v>0.4078</v>
       </c>
       <c r="P48" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.2043</v>
+        <v>0.1522</v>
       </c>
       <c r="R48" t="n">
-        <v>0.609</v>
+        <v>0.3</v>
       </c>
       <c r="S48" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="T48" t="n">
-        <v>0.719</v>
+        <v>0.41</v>
       </c>
       <c r="U48" t="n">
-        <v>2.44</v>
+        <v>1.82</v>
       </c>
       <c r="V48" t="n">
-        <v>1.0625</v>
+        <v>0.5625</v>
       </c>
       <c r="W48" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="X48" t="n">
-        <v>0.3895</v>
+        <v>0.2515</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.04511</v>
+        <v>0.03007</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.02083</v>
+        <v>0.01389</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.02482</v>
+        <v>0.65645</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.5457</v>
+        <v>0.4078</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.51241</v>
+        <v>0.32823</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.45527</v>
+        <v>0.28378</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.44</v>
+        <v>1.82</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.796</v>
+        <v>0.584</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.69</v>
+        <v>1.26</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="AN48" t="n">
-        <v>0.30622</v>
+        <v>0.21601</v>
       </c>
       <c r="AO48" t="n">
-        <v>0.30622</v>
+        <v>0.21601</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.61293</v>
+        <v>0.43251</v>
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>2501-L-12-12-FG</t>
+          <t>2501-L-06-06-FG</t>
         </is>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 1/16-12 JIC x 3/4-14 NPTF</t>
+          <t>90 deg Male Elbow, 9/16-18 JIC x 3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
@@ -8784,64 +8784,64 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>9/16-18 JIC</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-L-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N711 M 1 Size = 1.660 (table had empty); N3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P711 L 1 Size = 2.440 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R711 Hex Flat = 1.062 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S711 Side 1 ID = 0.609 (table had empty); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!X711 Side 2 ID = 0.719 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N3@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p24 2501-L-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 13/13 (M) and 12/13 (L) rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p24 2501-L-FG (same source as OMi, not a second source); JIC end: MS33656J (gen_straight2 JIC[12], VERIFIED) THDMAJ_B 1.0625; NPTF end ASME B1.20.3 (ms51500.NPTF[12]) THDMAJ_A 1.05; threads from the part number dashes (= catalog callouts); dims NOT taken from the non-FG Air-Way twin 2501-L-12-12 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s119 only (double-pass 21 rows); M leg matches verified 2501 family; N3 long leg single-source; JIC end VERIFIED (MS33656J) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-L-12-12 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p24 2501-L-FG on all five body values, same source), not from the non-FG twin 2501-L-12-12 | 2501L row folded into the 2501 master (user decision 2026-09-25) | hex A/F raised from Air-Way 1.062 to 1.0625 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0625 (round end flush with the flats by 0.0018; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M@DRIVE=1.14~1.140; N3@DRIVE=1.82~1.820; Y@REF=0.75~0.750; D@BORE=0.3~0.297; D1@BORE=0.41~0.406 | 2501L row folded into the 2501 master (user decision 2026-09-25)</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>2501-L-12-12-FG</t>
+          <t>2501-L-06-06-FG</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2501-L-16-16-FG</t>
+          <t>2501-L-08-08-FG</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.81</v>
+        <v>1.33</v>
       </c>
       <c r="C49" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="D49" t="n">
-        <v>0.65625</v>
+        <v>0.375</v>
       </c>
       <c r="E49" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4365</v>
+        <v>0.2837</v>
       </c>
       <c r="G49" t="n">
-        <v>0.5965</v>
+        <v>0.3295</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1292</v>
+        <v>0.0984</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1858</v>
+        <v>0.1546</v>
       </c>
       <c r="J49" t="n">
         <v>60</v>
@@ -8850,141 +8850,1541 @@
         <v>37</v>
       </c>
       <c r="L49" t="n">
-        <v>3.01</v>
+        <v>2.17</v>
       </c>
       <c r="M49" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="N49" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.40779</v>
       </c>
       <c r="O49" t="n">
-        <v>0.6828</v>
+        <v>0.5337</v>
       </c>
       <c r="P49" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q49" t="n">
+        <v>0.2163</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0.25209</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>0.50468</v>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>2501-L-08-08-FG</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>90 deg Male Elbow, 3/4-16 JIC x 1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>2501</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr">
+        <is>
+          <t>3/4-16 JIC</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-L-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N708 M 1 Size = 1.330 (table had empty); N3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P708 L 1 Size = 2.170 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R708 Hex Flat = 0.875 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S708 Side 1 ID = 0.391 (table had empty); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!X708 Side 2 ID = 0.531 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N3@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p24 2501-L-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 13/13 (M) and 12/13 (L) rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p24 2501-L-FG (same source as OMi, not a second source); JIC end: MS33656J (gen_straight2 JIC[8], VERIFIED) THDMAJ_B 0.75; NPTF end ASME B1.20.3 (ms51500.NPTF[8]) THDMAJ_A 0.84; threads from the part number dashes (= catalog callouts); dims NOT taken from the non-FG Air-Way twin 2501-L-08-08 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-L-08-08 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p24 2501-L-FG on all five body values, same source), not from the non-FG twin 2501-L-08-08 | 2501L row folded into the 2501 master (user decision 2026-09-25)</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>2501-L-08-08-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2501-L-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="J50" t="n">
+        <v>60</v>
+      </c>
+      <c r="K50" t="n">
+        <v>37</v>
+      </c>
+      <c r="L50" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.02482</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>0.61293</v>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>2501-L-12-12-FG</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>90 deg Male Elbow, 1 1/16-12 JIC x 3/4-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>2501</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-L-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N711 M 1 Size = 1.660 (table had empty); N3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P711 L 1 Size = 2.440 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R711 Hex Flat = 1.062 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S711 Side 1 ID = 0.609 (table had empty); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!X711 Side 2 ID = 0.719 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N3@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p24 2501-L-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 13/13 (M) and 12/13 (L) rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p24 2501-L-FG (same source as OMi, not a second source); JIC end: MS33656J (gen_straight2 JIC[12], VERIFIED) THDMAJ_B 1.0625; NPTF end ASME B1.20.3 (ms51500.NPTF[12]) THDMAJ_A 1.05; threads from the part number dashes (= catalog callouts); dims NOT taken from the non-FG Air-Way twin 2501-L-12-12 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-L-12-12 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p24 2501-L-FG on all five body values, same source), not from the non-FG twin 2501-L-12-12 | 2501L row folded into the 2501 master (user decision 2026-09-25) | hex A/F raised from Air-Way 1.062 to 1.0625 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0625 (round end flush with the flats by 0.0018; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>2501-L-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2501-L-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="J51" t="n">
+        <v>60</v>
+      </c>
+      <c r="K51" t="n">
+        <v>37</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.6415999999999999</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.6828</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="Q51" t="n">
         <v>0.2572</v>
       </c>
-      <c r="R49" t="n">
+      <c r="R51" t="n">
         <v>0.844</v>
       </c>
-      <c r="S49" t="n">
+      <c r="S51" t="n">
         <v>1.81</v>
       </c>
-      <c r="T49" t="n">
+      <c r="T51" t="n">
         <v>0.9379999999999999</v>
       </c>
-      <c r="U49" t="n">
+      <c r="U51" t="n">
         <v>3.01</v>
       </c>
-      <c r="V49" t="n">
+      <c r="V51" t="n">
         <v>1.3125</v>
       </c>
-      <c r="W49" t="n">
+      <c r="W51" t="n">
         <v>0.08333</v>
       </c>
-      <c r="X49" t="n">
+      <c r="X51" t="n">
         <v>0.4365</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="Y51" t="n">
         <v>0.04511</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="Z51" t="n">
         <v>0.02083</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AA51" t="n">
         <v>0.08333</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AB51" t="n">
         <v>1.2832</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AC51" t="n">
         <v>0.6828</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AD51" t="n">
         <v>0.08696</v>
       </c>
-      <c r="AE49" t="n">
+      <c r="AE51" t="n">
         <v>0.6415999999999999</v>
       </c>
-      <c r="AF49" t="n">
+      <c r="AF51" t="n">
         <v>0.57203</v>
       </c>
-      <c r="AG49" t="n">
+      <c r="AG51" t="n">
         <v>3.01</v>
       </c>
-      <c r="AH49" t="n">
+      <c r="AH51" t="n">
         <v>1.3125</v>
       </c>
-      <c r="AI49" t="n">
+      <c r="AI51" t="n">
         <v>0.899</v>
       </c>
-      <c r="AJ49" t="n">
+      <c r="AJ51" t="n">
         <v>1.3125</v>
       </c>
-      <c r="AK49" t="n">
+      <c r="AK51" t="n">
         <v>2.07</v>
       </c>
-      <c r="AL49" t="n">
+      <c r="AL51" t="n">
         <v>0.65625</v>
       </c>
-      <c r="AM49" t="n">
+      <c r="AM51" t="n">
         <v>0.65625</v>
       </c>
-      <c r="AN49" t="n">
+      <c r="AN51" t="n">
         <v>0.37839</v>
       </c>
-      <c r="AO49" t="n">
+      <c r="AO51" t="n">
         <v>0.37839</v>
       </c>
-      <c r="AP49" t="n">
+      <c r="AP51" t="n">
         <v>0.75727</v>
       </c>
-      <c r="AQ49" t="inlineStr">
+      <c r="AQ51" t="inlineStr">
         <is>
           <t>2501-L-16-16-FG</t>
         </is>
       </c>
-      <c r="AR49" t="inlineStr">
+      <c r="AR51" t="inlineStr">
         <is>
           <t>90 deg Male Elbow, 1 5/16-12 JIC x 1-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="AS49" t="inlineStr">
+      <c r="AS51" t="inlineStr">
         <is>
           <t>2501</t>
         </is>
       </c>
-      <c r="AT49" t="inlineStr">
+      <c r="AT51" t="inlineStr">
         <is>
           <t>1 5/16-12 JIC</t>
         </is>
       </c>
-      <c r="AU49" t="inlineStr">
+      <c r="AU51" t="inlineStr">
         <is>
           <t>1-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="AV49" t="inlineStr">
+      <c r="AV51" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AW49" t="inlineStr">
+      <c r="AW51" t="inlineStr">
         <is>
           <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-L-16-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N713 M 1 Size = 1.810 (table had empty); N3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P713 L 1 Size = 3.010 (table had empty); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R713 Hex Flat = 1.312 (table had empty); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!S713 Side 1 ID = 0.844 (table had empty); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!X713 Side 2 ID = 0.938 (table had empty) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N3@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p24 2501-L-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 13/13 (M) and 12/13 (L) rows, match/TFA_elbows.json, impact F1a, Q-B-ELBOW answered by the catalog); the same five body values are printed for this -FG part in Brennan TFA catalog p24 2501-L-FG (same source as OMi, not a second source); JIC end: MS33656J (gen_straight2 JIC[16], VERIFIED) THDMAJ_B 1.3125; NPTF end ASME B1.20.3 (ms51500.NPTF[16]) THDMAJ_A 1.315; threads from the part number dashes (= catalog callouts); dims NOT taken from the non-FG Air-Way twin 2501-L-16-16 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
+      <c r="AX51" t="inlineStr">
         <is>
           <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-L-16-16 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-02 (batch 15, staged): the -FG dimensions now come from OMi WebsitePartsInfo2026.xlsx for this -FG part (= Brennan TFA catalog p24 2501-L-FG on all five body values, same source), not from the non-FG twin 2501-L-16-16 | 2501L row folded into the 2501 master (user decision 2026-09-25) | hex A/F raised from Air-Way 1.312 to 1.3125 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3125 (round end proud of the flats by 0.0067; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr">
+      <c r="AY51" t="inlineStr">
         <is>
           <t>2501-L-16-16-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2501-LL-04-02-FG</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="J52" t="n">
+        <v>60</v>
+      </c>
+      <c r="K52" t="n">
+        <v>37</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.19657</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.1161</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0.02706</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.03704</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0.19657</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0.16694</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>0.12594</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0.12594</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>0.25238</v>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>2501-LL-04-02-FG</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>90 deg Male Elbow, 7/16-20 JIC x 1/8-27 NPTF</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>2501</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr">
+        <is>
+          <t>7/16-20 JIC</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>1/8-27 NPTF</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-04-02 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-02-FG col "M LGTH" = "0.890" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 538.9, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip (column mapping: REPORT.md, table 2501LL); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-02-FG col "L LGTH" = "1.560" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 538.9, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the male NPTF tip (column mapping: REPORT.md, table 2501LL); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-02-FG col "Y FLATS" = "0.438" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 538.9, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 2501LL); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-02-FG col "B1 DRILL" = "0.172" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 538.9, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore (column mapping: REPORT.md, table 2501LL); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-02-FG col "A2 DRILL" = "0.188" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 538.9, page verified True) [Brennan = yes 2026-10-18] - pipe drill (column mapping: REPORT.md, table 2501LL); THDMAJ_B@DRIVE: end library: male JIC -04 thread major = 0.4375 (gen_straight2 JIC[4] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p024-t02 thread columns (B1 SAE 37Deg 7/16-20, A2 NPTF 1/8-27) and OMi Items Side 1 / 2 / 3 Thread | FOLD: 2501-LL fold: forged hex arm runs on along the pipe leg to N4 minus the 5404 NPTF end length (Brennan 2501-LL-08-08-FG STEP, tools/measure/elbow90.py: arm 0..2.120 continuous, end 0.750 = ENDL[8]; measured at -08-08 only) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(the row's hex Y (its source: the start of this AxialSource), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-04-02 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate) | 2501-LL row folded into the 2501 master: Brennan 2501-LL-08-08-FG STEP (pilot) shows the forged hex arm simply running on along the pipe leg (Q-NEW-FOLD-2501LL, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>2501-LL-04-02-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2501-LL-04-04-FG</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="J53" t="n">
+        <v>60</v>
+      </c>
+      <c r="K53" t="n">
+        <v>37</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.1582</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0.02706</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0.16174</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0.16174</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>2501-LL-04-04-FG</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>90 deg Male Elbow, 7/16-20 JIC x 1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>2501</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr">
+        <is>
+          <t>7/16-20 JIC</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-04-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-04-FG col "M LGTH" = "1.050" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 549.0, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-04-FG col "L LGTH" = "2.070" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 549.0, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the pipe tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-04-FG col "Y FLATS" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 549.0, page verified True) [Brennan = yes 2026-10-18] - forged body hex across flats (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-04-FG col "B1 DRILL" = "0.172" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 549.0, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-04-FG col "A2 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 549.0, page verified True) [Brennan = yes 2026-10-18] - pipe drill (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); THDMAJ_B@DRIVE: end library: male JIC -04 thread major = 0.4375 (gen_straight2 JIC[4] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other 2501-LL rows); = OMi Items Side 1 / Side 2 Thread and Brennan TFA p.24 B1 SAE 37Deg / A2 NPTF | FOLD: 2501-LL fold: forged hex arm runs on along the pipe leg to N4 minus the 5404 NPTF end length (Brennan 2501-LL-08-08-FG STEP, tools/measure/elbow90.py: arm 0..2.120 continuous, end 0.750 = ENDL[8]; measured at -08-08 only) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(the row's hex Y (its source: the start of this AxialSource), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-04-04 dims are NOT assumed; confirm before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-04-04 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate) | 2501-LL row folded into the 2501 master: Brennan 2501-LL-08-08-FG STEP (pilot) shows the forged hex arm simply running on along the pipe leg (Q-NEW-FOLD-2501LL, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>2501-LL-04-04-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2501-LL-06-04-FG</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="J54" t="n">
+        <v>60</v>
+      </c>
+      <c r="K54" t="n">
+        <v>37</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.1582</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0.16188</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0.16188</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>2501-LL-06-04-FG</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>90 deg Male Elbow, 9/16-18 JIC x 1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>2501</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr">
+        <is>
+          <t>9/16-18 JIC</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-06-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-04-FG col "M LGTH" = "1.06" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 579.2, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-04-FG col "L LGTH" = "2.07" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 579.2, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the pipe tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-04-FG col "Y FLATS" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 579.2, page verified True) [Brennan = yes 2026-10-18] - forged body hex across flats (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-04-FG col "B1 DRILL" = "0.297" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 579.2, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-04-FG col "A2 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 579.2, page verified True) [Brennan = yes 2026-10-18] - pipe drill (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); THDMAJ_B@DRIVE: end library: male JIC -06 thread major = 0.5625 (gen_straight2 JIC[6] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other 2501-LL rows); = OMi Items Side 1 / Side 2 Thread and Brennan TFA p.24 B1 SAE 37Deg / A2 NPTF | FOLD: 2501-LL fold: forged hex arm runs on along the pipe leg to N4 minus the 5404 NPTF end length (Brennan 2501-LL-08-08-FG STEP, tools/measure/elbow90.py: arm 0..2.120 continuous, end 0.750 = ENDL[8]; measured at -08-08 only) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(the row's hex Y (its source: the start of this AxialSource), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-06-04 dims are NOT assumed; confirm before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-06-04 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate) | 2501-LL row folded into the 2501 master: Brennan 2501-LL-08-08-FG STEP (pilot) shows the forged hex arm simply running on along the pipe leg (Q-NEW-FOLD-2501LL, 2026-10-02) | hex A/F raised from the row's hex Y 0.562 to 0.5625 (JIC thread major; 2603HX rule)</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>2501-LL-06-04-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2501-LL-06-06-FG</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="J55" t="n">
+        <v>60</v>
+      </c>
+      <c r="K55" t="n">
+        <v>37</v>
+      </c>
+      <c r="L55" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>2501-LL-06-06-FG</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>90 deg Male Elbow, 9/16-18 JIC x 3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>2501</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr">
+        <is>
+          <t>9/16-18 JIC</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-06-FG col "M LGTH" = "1.14" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 589.3, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-06-FG col "L LGTH" = "2.42" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 589.3, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the pipe tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-06-FG col "Y FLATS" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 589.3, page verified True) [Brennan = yes 2026-10-18] - forged body hex across flats (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-06-FG col "B1 DRILL" = "0.297" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 589.3, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-06-FG col "A2 DRILL" = "0.406" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 589.3, page verified True) [Brennan = yes 2026-10-18] - pipe drill (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); THDMAJ_B@DRIVE: end library: male JIC -06 thread major = 0.5625 (gen_straight2 JIC[6] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other 2501-LL rows); = OMi Items Side 1 / Side 2 Thread and Brennan TFA p.24 B1 SAE 37Deg / A2 NPTF | FOLD: 2501-LL fold: forged hex arm runs on along the pipe leg to N4 minus the 5404 NPTF end length (Brennan 2501-LL-08-08-FG STEP, tools/measure/elbow90.py: arm 0..2.120 continuous, end 0.750 = ENDL[8]; measured at -08-08 only) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(the row's hex Y (its source: the start of this AxialSource), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-06-06 dims are NOT assumed; confirm before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-06-06 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate) | 2501-LL row folded into the 2501 master: Brennan 2501-LL-08-08-FG STEP (pilot) shows the forged hex arm simply running on along the pipe leg (Q-NEW-FOLD-2501LL, 2026-10-02)</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>2501-LL-06-06-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2501-LL-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="J56" t="n">
+        <v>60</v>
+      </c>
+      <c r="K56" t="n">
+        <v>37</v>
+      </c>
+      <c r="L56" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.02482</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>0.61293</v>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>2501-LL-12-12-FG</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>90 deg Male Elbow, 1 1/16-12 JIC x 3/4-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>2501</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "M LGTH" = "1.660" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "L LGTH" = "3.280" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the pipe tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - forged body hex across flats (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "B1 DRILL" = "0.609" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "A2 DRILL" = "0.719" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - pipe drill (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); THDMAJ_B@DRIVE: end library: male JIC -12 thread major = 1.0625 (gen_straight2 JIC[12] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -12 NPTF thread = 1.05 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[12], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other 2501-LL rows); = OMi Items Side 1 / Side 2 Thread and Brennan TFA p.24 B1 SAE 37Deg / A2 NPTF | FOLD: 2501-LL fold: forged hex arm runs on along the pipe leg to N4 minus the 5404 NPTF end length (Brennan 2501-LL-08-08-FG STEP, tools/measure/elbow90.py: arm 0..2.120 continuous, end 0.750 = ENDL[8]; measured at -08-08 only) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(the row's hex Y (its source: the start of this AxialSource), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-12-12 dims are NOT assumed; confirm before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-12-12 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate) | 2501-LL row folded into the 2501 master: Brennan 2501-LL-08-08-FG STEP (pilot) shows the forged hex arm simply running on along the pipe leg (Q-NEW-FOLD-2501LL, 2026-10-02) | hex A/F raised from the row's hex Y 1.062 to 1.0625 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0625 (round end flush with the flats by 0.0018; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>2501-LL-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2501-LL-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="J57" t="n">
+        <v>60</v>
+      </c>
+      <c r="K57" t="n">
+        <v>37</v>
+      </c>
+      <c r="L57" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.6415999999999999</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.6828</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="U57" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.2832</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0.6828</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0.6415999999999999</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0.57203</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>0.75727</v>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>2501-LL-16-16-FG</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>90 deg Male Elbow, 1 5/16-12 JIC x 1-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>2501</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr">
+        <is>
+          <t>1 5/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-16-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-16-16-FG col "M LGTH" = "1.81" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.1, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-16-16-FG col "L LGTH" = "4.05" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.1, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the pipe tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-16-16-FG col "Y FLATS" = "1.312" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.1, page verified True) [Brennan = yes 2026-10-18] - forged body hex across flats (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-16-16-FG col "B1 DRILL" = "0.844" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.1, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-16-16-FG col "A2 DRILL" = "0.938" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.1, page verified True) [Brennan = yes 2026-10-18] - pipe drill (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); THDMAJ_B@DRIVE: end library: male JIC -16 thread major = 1.3125 (gen_straight2 JIC[16] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other 2501-LL rows); = OMi Items Side 1 / Side 2 Thread and Brennan TFA p.24 B1 SAE 37Deg / A2 NPTF | FOLD: 2501-LL fold: forged hex arm runs on along the pipe leg to N4 minus the 5404 NPTF end length (Brennan 2501-LL-08-08-FG STEP, tools/measure/elbow90.py: arm 0..2.120 continuous, end 0.750 = ENDL[8]; measured at -08-08 only) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(the row's hex Y (its source: the start of this AxialSource), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-16-16 dims are NOT assumed; confirm before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-16-16 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate) | 2501-LL row folded into the 2501 master: Brennan 2501-LL-08-08-FG STEP (pilot) shows the forged hex arm simply running on along the pipe leg (Q-NEW-FOLD-2501LL, 2026-10-02) | hex A/F raised from the row's hex Y 1.312 to 1.3125 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3125 (round end proud of the flats by 0.0067; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>2501-LL-16-16-FG</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_2501_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2501_SW2.xlsx
@@ -1215,7 +1215,7 @@
         <v>37</v>
       </c>
       <c r="L5" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="M5" t="n">
         <v>0.22</v>
@@ -1242,7 +1242,7 @@
         <v>0.19</v>
       </c>
       <c r="U5" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="V5" t="n">
         <v>0.4375</v>
@@ -1278,7 +1278,7 @@
         <v>0.16694</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="AH5" t="n">
         <v>0.44</v>
@@ -1290,7 +1290,7 @@
         <v>0.44</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="AL5" t="n">
         <v>0.22</v>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>was "VERIFIED" (vote text in the wrong column); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P661 L 1 Size = 0.78 (table had 0.76 = Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F45D, Q-B-ELBOW answered by the catalog); THDMAJ_A@DRIVE: 0.78 -&gt; 0.4375 (column-shift repair; -04 JIC 7/16-20, gen_straight2 JIC[4]); M / Y / D / D1 = OMi Items!N661 / R661 / S661 / X661 (0.89 equal; the table values 0.44 / 0.17 / 0.19 differ from OMi 0.438 / 0.172 / 0.188 by rounding only and are kept, user 2026-09-25); JIC end MS33656J = Brennan (VERIFIED), NPTF ASME B1.20.3 [batch 15, 2026-10-02, staged for review] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>was "VERIFIED" (vote text in the wrong column); N@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P661 L 1 Size = 0.78 (table had 0.76 = Air-Way) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; leg columns: OMi "M 1 Size" = M@DRIVE (first-dash male JIC leg), "L 1 Size" = N@DRIVE (second-dash male pipe leg) - settled by the Brennan TFA catalog p23 2501-FG drawing letters (M = JIC tip to the pipe-leg axis, L = pipe tip to the JIC-leg axis; OMi M 1 / L 1 = catalog M / L on 44/44 rows, match/TFA_elbows.json, impact F45D, Q-B-ELBOW answered by the catalog); THDMAJ_A@DRIVE: 0.78 -&gt; 0.4375 (column-shift repair; -04 JIC 7/16-20, gen_straight2 JIC[4]); M / Y / D / D1 = OMi Items!N661 / R661 / S661 / X661 (0.89 equal; the table values 0.44 / 0.17 / 0.19 differ from OMi 0.438 / 0.172 / 0.188 by rounding only and are kept, user 2026-09-25); JIC end MS33656J = Brennan (VERIFIED), NPTF ASME B1.20.3 [batch 15, 2026-10-02, staged for review]; N@DRIVE: Air-Way 0.76 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.78) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>CONFLICT vs MS51504 - see workbook | 2026-10-02 (batch 15, staged): Air-Way N 0.76 vs MS51504 .780 conflict settled by the OMi-first rule - OMi L 1 Size 0.78 (Items!P661; = Brennan TFA catalog p23 L 0.78); THDMAJ_A held the shifted vote value 0.78 -&gt; repaired to 0.4375 (-04 JIC); Q-CONFLICT-2501-04-02-FG not needed (impact F45D)</t>
+          <t>CONFLICT vs MS51504 - see workbook | 2026-10-02 (batch 15, staged): Air-Way N 0.76 vs MS51504 .780 conflict settled by the OMi-first rule - OMi L 1 Size 0.78 (Items!P661; = Brennan TFA catalog p23 L 0.78); THDMAJ_A held the shifted vote value 0.78 -&gt; repaired to 0.4375 (-04 JIC); Q-CONFLICT-2501-04-02-FG not needed (impact F45D) | 2026-10-20 Air-Way first: N@DRIVE OMi/Brennan 0.78 -&gt; Air-Way 0.76</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="C38" t="n">
         <v>0.9399999999999999</v>
@@ -6956,7 +6956,7 @@
         <v>1.08</v>
       </c>
       <c r="S38" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="T38" t="n">
         <v>1.5</v>
@@ -7004,7 +7004,7 @@
         <v>1.88</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.242</v>
+        <v>1.342</v>
       </c>
       <c r="AJ38" t="n">
         <v>1.88</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504); M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N695 = 2.20 (table had 2.3) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504); M@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N695 = 2.20 (table had 2.3) [user 2026-10-18 A19]; M@DRIVE: Air-Way 2.3 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.2) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): M@DRIVE 2.3 -&gt; OMi 2.20 (Items!N695, M071) | leg 2: male NPTF thread dia at L2 1.9109 vs hex flats 1.8800 (round end proud of the flats by 0.0154; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): M@DRIVE 2.3 -&gt; OMi 2.20 (Items!N695, M071) | 2026-10-20 Air-Way first: M@DRIVE OMi/Brennan 2.2 -&gt; Air-Way 2.3 | leg 2: male NPTF thread dia at L2 1.9109 vs hex flats 1.8800 (round end proud of the flats by 0.0154; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R698 Hex Flat = 1.875 (table had 1.81) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>JIC end: MS33656J==Brennan (VERIFIED); NPTF: ASME B1.20.3; legs: Air-Way (FG corroborated MS51504); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R698 Hex Flat = 1.875 (table had 1.81) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; Y@REF: Air-Way 1.81 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>leg 2: male NPTF thread dia at L2 1.9109 vs hex flats 1.8750 (round end proud of the flats by 0.0179; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>2026-10-20 Air-Way first: Y@REF OMi/Brennan 1.875 -&gt; Air-Way 1.81 | hex A/F raised from Air-Way 1.81 to 1.8750 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.9109 vs hex flats 1.8750 (round end proud of the flats by 0.0179; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -7999,7 +7999,7 @@
         <v>3.06</v>
       </c>
       <c r="T44" t="n">
-        <v>1.938</v>
+        <v>1.86</v>
       </c>
       <c r="U44" t="n">
         <v>3</v>
@@ -8099,12 +8099,12 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>was "VERIFIED" (vote text in the wrong column); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R701 Hex Flat = 2.500 (table had 1.938, the voted drill shifted into this column); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X701 Side 2 ID = 1.938 (table had 1.86) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; legs/bore/ends as the other 2501 -FG rows (Air-Way legs, JIC end MS33656J = Brennan, NPTF ASME B1.20.3) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>was "VERIFIED" (vote text in the wrong column); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R701 Hex Flat = 2.500 (table had 1.938, the voted drill shifted into this column); D1@DRILL: OMi WebsitePartsInfo2026.xlsx Items!X701 Side 2 ID = 1.938 (table had 1.86) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; legs/bore/ends as the other 2501 -FG rows (Air-Way legs, JIC end MS33656J = Brennan, NPTF ASME B1.20.3); D1@DRILL: Air-Way 1.86 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.938) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>CONFLICT vs MS51504 - see workbook | 2026-09-25: Air-Way vs MS51504 drill conflict resolved by the OMi-first rule (OMi Side 2 ID 1.938 = MS51504 + Brennan); Y@REF held the voted drill 1.938 (column shift, audit 3.5) - OMi Hex Flat 2.500 = Air-Way printed Y 2.50</t>
+          <t>CONFLICT vs MS51504 - see workbook | 2026-09-25: Air-Way vs MS51504 drill conflict resolved by the OMi-first rule (OMi Side 2 ID 1.938 = MS51504 + Brennan); Y@REF held the voted drill 1.938 (column shift, audit 3.5) - OMi Hex Flat 2.500 = Air-Way printed Y 2.50 | 2026-10-20 Air-Way first: D1@DRILL OMi/Brennan 1.938 -&gt; Air-Way 1.86</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -8150,7 +8150,7 @@
         <v>37</v>
       </c>
       <c r="L45" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="M45" t="n">
         <v>0.22</v>
@@ -8177,7 +8177,7 @@
         <v>0.19</v>
       </c>
       <c r="U45" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="V45" t="n">
         <v>0.4375</v>
@@ -8213,7 +8213,7 @@
         <v>0.16694</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AH45" t="n">
         <v>0.44</v>
@@ -8225,7 +8225,7 @@
         <v>0.44</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AL45" t="n">
         <v>0.22</v>
@@ -8274,12 +8274,12 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Air-Way s119 only (double-pass 21 rows); M leg matches verified 2501 family; N3 long leg single-source; JIC end VERIFIED (MS33656J); N3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P703 = 1.170 (table had 1.19) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s119 only (double-pass 21 rows); M leg matches verified 2501 family; N3 long leg single-source; JIC end VERIFIED (MS33656J); N3@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P703 = 1.170 (table had 1.19) [user 2026-10-18 A19]; N3@DRIVE: Air-Way 1.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.17) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>M matches verified 2501 M family | A19 (user 2026-10-18, group 2 settled): N3@DRIVE 1.19 -&gt; OMi 1.170 (Items!P703, M077) | 2501L row folded into the 2501 master (user decision 2026-09-25)</t>
+          <t>M matches verified 2501 M family | A19 (user 2026-10-18, group 2 settled): N3@DRIVE 1.19 -&gt; OMi 1.170 (Items!P703, M077) | 2026-10-20 Air-Way first: N3@DRIVE OMi/Brennan 1.17 -&gt; Air-Way 1.19 | 2501L row folded into the 2501 master (user decision 2026-09-25)</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_2501_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2501_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10041,32 +10041,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2501-LL-12-12-FG</t>
+          <t>2501-LL-08-08-FG</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="C56" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="D56" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="E56" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="G56" t="n">
-        <v>0.4715</v>
+        <v>0.3295</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1299</v>
+        <v>0.0984</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="J56" t="n">
         <v>60</v>
@@ -10075,106 +10075,106 @@
         <v>37</v>
       </c>
       <c r="L56" t="n">
-        <v>3.28</v>
+        <v>2.87</v>
       </c>
       <c r="M56" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="N56" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="O56" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="P56" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.2043</v>
+        <v>0.2163</v>
       </c>
       <c r="R56" t="n">
-        <v>0.609</v>
+        <v>0.391</v>
       </c>
       <c r="S56" t="n">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="T56" t="n">
-        <v>0.719</v>
+        <v>0.531</v>
       </c>
       <c r="U56" t="n">
-        <v>3.28</v>
+        <v>2.87</v>
       </c>
       <c r="V56" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="W56" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="X56" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.02482</v>
+        <v>0.81557</v>
       </c>
       <c r="AC56" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="AD56" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="AE56" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="AF56" t="n">
-        <v>0.45527</v>
+        <v>0.35064</v>
       </c>
       <c r="AG56" t="n">
-        <v>3.28</v>
+        <v>2.87</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.796</v>
+        <v>0.673</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="AK56" t="n">
-        <v>2.53</v>
+        <v>2.12</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="AN56" t="n">
-        <v>0.30622</v>
+        <v>0.25209</v>
       </c>
       <c r="AO56" t="n">
-        <v>0.30622</v>
+        <v>0.25209</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.61293</v>
+        <v>0.50468</v>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>2501-LL-12-12-FG</t>
+          <t>2501-LL-08-08-FG</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>90 deg Male Elbow, 1 1/16-12 JIC x 3/4-14 NPTF</t>
+          <t>90 deg Male Elbow, 3/4-16 JIC x 1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
@@ -10184,12 +10184,12 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>3/4-16 JIC</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -10199,49 +10199,49 @@
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "M LGTH" = "1.660" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "L LGTH" = "3.280" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the pipe tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - forged body hex across flats (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "B1 DRILL" = "0.609" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "A2 DRILL" = "0.719" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - pipe drill (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); THDMAJ_B@DRIVE: end library: male JIC -12 thread major = 1.0625 (gen_straight2 JIC[12] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -12 NPTF thread = 1.05 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[12], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other 2501-LL rows); = OMi Items Side 1 / Side 2 Thread and Brennan TFA p.24 B1 SAE 37Deg / A2 NPTF | FOLD: 2501-LL fold: forged hex arm runs on along the pipe leg to N4 minus the 5404 NPTF end length (Brennan 2501-LL-08-08-FG STEP, tools/measure/elbow90.py: arm 0..2.120 continuous, end 0.750 = ENDL[8]; measured at -08-08 only) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(the row's hex Y (its source: the start of this AxialSource), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-21] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-21 (batch 19 C, staged): Brennan allowed (user 2026-10-18 "yes use brennan but still differentiate"); Air-Way prints no value for this part number, OMi's website file gives no dimension; sizes from the Brennan TFA catalog, each checked on the part's OWN Brennan STEP (09_STEP_FILES/BRENNAN_2501-LL-08-08-FG.stp, every value equal to the catalog within 0.005); end details from the end library: M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-08-08-FG col "M LGTH" = "1.330" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 629.6, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip; own STEP: JIC tip 1.33, JIC end 0.657 = JIC[8] chain (C_ownstep/measure/2501-LL-08-08-FG.txt (elbow90.py / nptfm40.py --leg)); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-08-08-FG col "L LGTH" = "2.870" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 629.6, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the NPTF tip; own STEP: pipe tip 2.87, male NPTF end 0.75 = ENDL[8], arm runs on to the end (C_ownstep/measure/2501-LL-08-08-FG.txt (elbow90.py / nptfm40.py --leg)); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-08-08-FG col "Y FLATS" = "0.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 629.6, page verified True) [Brennan = yes 2026-10-18] - forged body hex; own STEP: flats 0.875 on both arms (C_ownstep/measure/2501-LL-08-08-FG.txt (elbow90.py / nptfm40.py --leg)); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-08-08-FG col "B1 DRILL" = "0.391" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 629.6, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore; own STEP: JIC-leg bore 0.391 (C_ownstep/measure/2501-LL-08-08-FG.txt (elbow90.py / nptfm40.py --leg)); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-08-08-FG col "A2 DRILL" = "0.531" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 629.6, page verified True) [Brennan = yes 2026-10-18] - pipe drill; own STEP: pipe-leg bore 0.531 (C_ownstep/measure/2501-LL-08-08-FG.txt (elbow90.py / nptfm40.py --leg)); THDMAJ_B@DRIVE: end library: male JIC -08 thread major = 0.75 (gen_straight2 JIC[8] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08] | FOLD: 2501-LL fold: forged hex arm runs on along the pipe leg to N4 minus the 5404 NPTF end length (Brennan 2501-LL-08-08-FG STEP, tools/measure/elbow90.py: arm 0..2.120 continuous, end 0.750 = ENDL[8]; measured at -08-08 only) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(the row's hex Y (its source: the start of this AxialSource), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-12-12 dims are NOT assumed; confirm before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-12-12 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate) | 2501-LL row folded into the 2501 master: Brennan 2501-LL-08-08-FG STEP (pilot) shows the forged hex arm simply running on along the pipe leg (Q-NEW-FOLD-2501LL, 2026-10-02) | hex A/F raised from the row's hex Y 1.062 to 1.0625 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0625 (round end flush with the flats by 0.0018; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-08-08 dims are NOT assumed; confirm before modelling | 2026-10-21 batch 19 C (staged, not shipped): filled from the Brennan TFA catalog, checked on the own STEP (tools/_out/batch19_20261021/C_ownstep/measure); marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate). Cross-check only: Air-Way 2501-LL-8-8 (plain): M 1.31 N4 2.88 Y 0.94 D 0.39 D1 0.53 (Y differs: forged flats 0.875) | 2501-LL row folded into the 2501 master: Brennan 2501-LL-08-08-FG STEP (pilot) shows the forged hex arm simply running on along the pipe leg (Q-NEW-FOLD-2501LL, 2026-10-02)</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>2501-LL-12-12-FG</t>
+          <t>2501-LL-08-08-FG</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2501-LL-16-16-FG</t>
+          <t>2501-LL-12-12-FG</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="C57" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="D57" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="E57" t="n">
         <v>0.125</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="J57" t="n">
         <v>60</v>
@@ -10250,43 +10250,43 @@
         <v>37</v>
       </c>
       <c r="L57" t="n">
-        <v>4.05</v>
+        <v>3.28</v>
       </c>
       <c r="M57" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="N57" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="O57" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="P57" t="n">
         <v>1.7899</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.2572</v>
+        <v>0.2043</v>
       </c>
       <c r="R57" t="n">
-        <v>0.844</v>
+        <v>0.609</v>
       </c>
       <c r="S57" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="T57" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.719</v>
       </c>
       <c r="U57" t="n">
-        <v>4.05</v>
+        <v>3.28</v>
       </c>
       <c r="V57" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="W57" t="n">
         <v>0.08333</v>
       </c>
       <c r="X57" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="Y57" t="n">
         <v>0.04511</v>
@@ -10298,91 +10298,266 @@
         <v>0.08333</v>
       </c>
       <c r="AB57" t="n">
+        <v>1.02482</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>0.61293</v>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>2501-LL-12-12-FG</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>90 deg Male Elbow, 1 1/16-12 JIC x 3/4-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>2501</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "M LGTH" = "1.660" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "L LGTH" = "3.280" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the pipe tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - forged body hex across flats (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "B1 DRILL" = "0.609" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "A2 DRILL" = "0.719" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - pipe drill (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); THDMAJ_B@DRIVE: end library: male JIC -12 thread major = 1.0625 (gen_straight2 JIC[12] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -12 NPTF thread = 1.05 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[12], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other 2501-LL rows); = OMi Items Side 1 / Side 2 Thread and Brennan TFA p.24 B1 SAE 37Deg / A2 NPTF | FOLD: 2501-LL fold: forged hex arm runs on along the pipe leg to N4 minus the 5404 NPTF end length (Brennan 2501-LL-08-08-FG STEP, tools/measure/elbow90.py: arm 0..2.120 continuous, end 0.750 = ENDL[8]; measured at -08-08 only) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(the row's hex Y (its source: the start of this AxialSource), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-12-12 dims are NOT assumed; confirm before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-12-12 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate) | 2501-LL row folded into the 2501 master: Brennan 2501-LL-08-08-FG STEP (pilot) shows the forged hex arm simply running on along the pipe leg (Q-NEW-FOLD-2501LL, 2026-10-02) | hex A/F raised from the row's hex Y 1.062 to 1.0625 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.0589 vs hex flats 1.0625 (round end flush with the flats by 0.0018; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>2501-LL-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2501-LL-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="J58" t="n">
+        <v>60</v>
+      </c>
+      <c r="K58" t="n">
+        <v>37</v>
+      </c>
+      <c r="L58" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.6415999999999999</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.6828</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="U58" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AB58" t="n">
         <v>1.2832</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AC58" t="n">
         <v>0.6828</v>
       </c>
-      <c r="AD57" t="n">
+      <c r="AD58" t="n">
         <v>0.08696</v>
       </c>
-      <c r="AE57" t="n">
+      <c r="AE58" t="n">
         <v>0.6415999999999999</v>
       </c>
-      <c r="AF57" t="n">
+      <c r="AF58" t="n">
         <v>0.57203</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AG58" t="n">
         <v>4.05</v>
       </c>
-      <c r="AH57" t="n">
+      <c r="AH58" t="n">
         <v>1.3125</v>
       </c>
-      <c r="AI57" t="n">
+      <c r="AI58" t="n">
         <v>0.899</v>
       </c>
-      <c r="AJ57" t="n">
+      <c r="AJ58" t="n">
         <v>1.3125</v>
       </c>
-      <c r="AK57" t="n">
+      <c r="AK58" t="n">
         <v>3.11</v>
       </c>
-      <c r="AL57" t="n">
+      <c r="AL58" t="n">
         <v>0.65625</v>
       </c>
-      <c r="AM57" t="n">
+      <c r="AM58" t="n">
         <v>0.65625</v>
       </c>
-      <c r="AN57" t="n">
+      <c r="AN58" t="n">
         <v>0.37839</v>
       </c>
-      <c r="AO57" t="n">
+      <c r="AO58" t="n">
         <v>0.37839</v>
       </c>
-      <c r="AP57" t="n">
+      <c r="AP58" t="n">
         <v>0.75727</v>
       </c>
-      <c r="AQ57" t="inlineStr">
+      <c r="AQ58" t="inlineStr">
         <is>
           <t>2501-LL-16-16-FG</t>
         </is>
       </c>
-      <c r="AR57" t="inlineStr">
+      <c r="AR58" t="inlineStr">
         <is>
           <t>90 deg Male Elbow, 1 5/16-12 JIC x 1-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="AS57" t="inlineStr">
+      <c r="AS58" t="inlineStr">
         <is>
           <t>2501</t>
         </is>
       </c>
-      <c r="AT57" t="inlineStr">
+      <c r="AT58" t="inlineStr">
         <is>
           <t>1 5/16-12 JIC</t>
         </is>
       </c>
-      <c r="AU57" t="inlineStr">
+      <c r="AU58" t="inlineStr">
         <is>
           <t>1-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="AV57" t="inlineStr">
+      <c r="AV58" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AW57" t="inlineStr">
+      <c r="AW58" t="inlineStr">
         <is>
           <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-16-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-16-16-FG col "M LGTH" = "1.81" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.1, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-16-16-FG col "L LGTH" = "4.05" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.1, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the pipe tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-16-16-FG col "Y FLATS" = "1.312" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.1, page verified True) [Brennan = yes 2026-10-18] - forged body hex across flats (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-16-16-FG col "B1 DRILL" = "0.844" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.1, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-16-16-FG col "A2 DRILL" = "0.938" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.1, page verified True) [Brennan = yes 2026-10-18] - pipe drill (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); THDMAJ_B@DRIVE: end library: male JIC -16 thread major = 1.3125 (gen_straight2 JIC[16] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other 2501-LL rows); = OMi Items Side 1 / Side 2 Thread and Brennan TFA p.24 B1 SAE 37Deg / A2 NPTF | FOLD: 2501-LL fold: forged hex arm runs on along the pipe leg to N4 minus the 5404 NPTF end length (Brennan 2501-LL-08-08-FG STEP, tools/measure/elbow90.py: arm 0..2.120 continuous, end 0.750 = ENDL[8]; measured at -08-08 only) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(the row's hex Y (its source: the start of this AxialSource), JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
+      <c r="AX58" t="inlineStr">
         <is>
           <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-16-16 dims are NOT assumed; confirm before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-16-16 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate) | 2501-LL row folded into the 2501 master: Brennan 2501-LL-08-08-FG STEP (pilot) shows the forged hex arm simply running on along the pipe leg (Q-NEW-FOLD-2501LL, 2026-10-02) | hex A/F raised from the row's hex Y 1.312 to 1.3125 (JIC thread major; 2603HX rule); leg 2: male NPTF thread dia at L2 1.3259 vs hex flats 1.3125 (round end proud of the flats by 0.0067; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr">
+      <c r="AY58" t="inlineStr">
         <is>
           <t>2501-LL-16-16-FG</t>
         </is>
